--- a/upload/orgao2026.xlsx
+++ b/upload/orgao2026.xlsx
@@ -493,19 +493,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>22415131.08</v>
+        <v>22915657.51</v>
       </c>
       <c r="F2" t="n">
-        <v>16221742.57</v>
+        <v>16496274.91</v>
       </c>
       <c r="G2" t="n">
-        <v>14787594.36</v>
+        <v>14899520.38</v>
       </c>
       <c r="H2" t="n">
         <v>2727880.95</v>
       </c>
       <c r="I2" t="n">
-        <v>216944688.94</v>
+        <v>216945133.94</v>
       </c>
     </row>
     <row r="3">
@@ -526,13 +526,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1758306.07</v>
+        <v>1986291.21</v>
       </c>
       <c r="F3" t="n">
-        <v>1601588.54</v>
+        <v>1601658.7</v>
       </c>
       <c r="G3" t="n">
-        <v>1379722.12</v>
+        <v>1379790.37</v>
       </c>
       <c r="H3" t="n">
         <v>60903.67</v>
@@ -559,13 +559,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>178896103.47</v>
+        <v>178948067.63</v>
       </c>
       <c r="F4" t="n">
-        <v>109545332.47</v>
+        <v>110496155.24</v>
       </c>
       <c r="G4" t="n">
-        <v>98750058.11</v>
+        <v>99521480.12</v>
       </c>
       <c r="H4" t="n">
         <v>35391637.95</v>
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2860809.88</v>
+        <v>2861063.88</v>
       </c>
       <c r="F5" t="n">
-        <v>1710660.75</v>
+        <v>1762924.14</v>
       </c>
       <c r="G5" t="n">
-        <v>1473770.81</v>
+        <v>1523539.95</v>
       </c>
       <c r="H5" t="n">
         <v>706301.5699999999</v>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2497227.64</v>
+        <v>2499067.64</v>
       </c>
       <c r="F6" t="n">
-        <v>1451380.33</v>
+        <v>1455598.88</v>
       </c>
       <c r="G6" t="n">
-        <v>1362028.33</v>
+        <v>1366243.16</v>
       </c>
       <c r="H6" t="n">
         <v>154717.57</v>
@@ -658,13 +658,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>24811305.35</v>
+        <v>25002305.35</v>
       </c>
       <c r="F7" t="n">
-        <v>18556561.21</v>
+        <v>19790080.52</v>
       </c>
       <c r="G7" t="n">
-        <v>16731304.3</v>
+        <v>17519267.59</v>
       </c>
       <c r="H7" t="n">
         <v>2353030.07</v>
@@ -691,19 +691,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>77772291.09</v>
+        <v>79863957.14</v>
       </c>
       <c r="F8" t="n">
-        <v>30773321.07</v>
+        <v>33889776.63</v>
       </c>
       <c r="G8" t="n">
-        <v>27854296.19</v>
+        <v>29369112.68</v>
       </c>
       <c r="H8" t="n">
-        <v>45834152.39</v>
+        <v>51118822.19</v>
       </c>
       <c r="I8" t="n">
-        <v>47131914.41</v>
+        <v>49029933.96</v>
       </c>
     </row>
     <row r="9">
@@ -727,7 +727,7 @@
         <v>3484649.64</v>
       </c>
       <c r="F9" t="n">
-        <v>2695846.6</v>
+        <v>2700019.98</v>
       </c>
       <c r="G9" t="n">
         <v>2602959.85</v>
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>81849575.48999999</v>
+        <v>83451344.81</v>
       </c>
       <c r="F10" t="n">
-        <v>72661047.7</v>
+        <v>76749035.73999999</v>
       </c>
       <c r="G10" t="n">
-        <v>63546344.13</v>
+        <v>64331542.04</v>
       </c>
       <c r="H10" t="n">
         <v>14925708.98</v>
       </c>
       <c r="I10" t="n">
-        <v>13881706.51</v>
+        <v>13889226.51</v>
       </c>
     </row>
     <row r="11">
@@ -790,19 +790,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1561236884.63</v>
+        <v>1621116303.32</v>
       </c>
       <c r="F11" t="n">
-        <v>824490142.15</v>
+        <v>834816709.8</v>
       </c>
       <c r="G11" t="n">
-        <v>797316689.8200001</v>
+        <v>814730941.02</v>
       </c>
       <c r="H11" t="n">
-        <v>334598887.77</v>
+        <v>338223224.55</v>
       </c>
       <c r="I11" t="n">
-        <v>340409119.02</v>
+        <v>342813777.57</v>
       </c>
     </row>
     <row r="12">
@@ -823,13 +823,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>33881959.45</v>
+        <v>34227344.15</v>
       </c>
       <c r="F12" t="n">
-        <v>10198029.11</v>
+        <v>10340289.26</v>
       </c>
       <c r="G12" t="n">
-        <v>9409144.609999999</v>
+        <v>9542932.08</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -918,13 +918,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>210407094.06</v>
+        <v>243357094.6</v>
       </c>
       <c r="F15" t="n">
-        <v>210407094.06</v>
+        <v>243357094.6</v>
       </c>
       <c r="G15" t="n">
-        <v>210407094.06</v>
+        <v>243357094.6</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>17658291.2</v>
+        <v>19634354.31</v>
       </c>
       <c r="F16" t="n">
-        <v>17658291.2</v>
+        <v>19634354.31</v>
       </c>
       <c r="G16" t="n">
-        <v>17658291.2</v>
+        <v>19634354.31</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -999,13 +999,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>85431443.5</v>
+        <v>98640447.63</v>
       </c>
       <c r="F18" t="n">
-        <v>85431443.5</v>
+        <v>98640447.63</v>
       </c>
       <c r="G18" t="n">
-        <v>85431443.5</v>
+        <v>98640447.63</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8645474.49</v>
+        <v>8668649.49</v>
       </c>
       <c r="F19" t="n">
-        <v>4390380.98</v>
+        <v>4402544.98</v>
       </c>
       <c r="G19" t="n">
-        <v>4020702.75</v>
+        <v>4030056.44</v>
       </c>
       <c r="H19" t="n">
         <v>1040158.72</v>
@@ -1064,10 +1064,10 @@
         <v>358206</v>
       </c>
       <c r="F20" t="n">
-        <v>212512.09</v>
+        <v>223427.58</v>
       </c>
       <c r="G20" t="n">
-        <v>200780.62</v>
+        <v>211696.11</v>
       </c>
       <c r="H20" t="n">
         <v>30324.78</v>
@@ -1094,13 +1094,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>918523.89</v>
+        <v>1004317.92</v>
       </c>
       <c r="F21" t="n">
-        <v>749432.03</v>
+        <v>838104.04</v>
       </c>
       <c r="G21" t="n">
-        <v>621295.3</v>
+        <v>693062.3</v>
       </c>
       <c r="H21" t="n">
         <v>97349.38</v>
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>19082553.74</v>
+        <v>19017448.76</v>
       </c>
       <c r="F22" t="n">
-        <v>16420623.95</v>
+        <v>16485291.12</v>
       </c>
       <c r="G22" t="n">
-        <v>14435895.25</v>
+        <v>14689413.44</v>
       </c>
       <c r="H22" t="n">
         <v>4345882.84</v>
@@ -1160,13 +1160,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>8853290.779999999</v>
+        <v>8970870.439999999</v>
       </c>
       <c r="F23" t="n">
-        <v>7943980.07</v>
+        <v>8009583.65</v>
       </c>
       <c r="G23" t="n">
-        <v>6994334.95</v>
+        <v>7062983.28</v>
       </c>
       <c r="H23" t="n">
         <v>1741057.76</v>
@@ -1202,10 +1202,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1921024.46</v>
+        <v>2122233.46</v>
       </c>
       <c r="I24" t="n">
-        <v>1828815.27</v>
+        <v>2020366.24</v>
       </c>
     </row>
     <row r="25">
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>11010371.13</v>
+        <v>11280695.13</v>
       </c>
       <c r="F26" t="n">
-        <v>4402545.3</v>
+        <v>4407081.74</v>
       </c>
       <c r="G26" t="n">
-        <v>4352573.91</v>
+        <v>4357523.1</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -1284,13 +1284,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>9417855.18</v>
+        <v>9829781.16</v>
       </c>
       <c r="F27" t="n">
-        <v>9060070.529999999</v>
+        <v>9424323.33</v>
       </c>
       <c r="G27" t="n">
-        <v>7626121.2</v>
+        <v>7650353.71</v>
       </c>
       <c r="H27" t="n">
         <v>1102595.36</v>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>8382802.49</v>
+        <v>9063969.41</v>
       </c>
       <c r="F28" t="n">
-        <v>7013936.1</v>
+        <v>7103215.07</v>
       </c>
       <c r="G28" t="n">
-        <v>6297041.02</v>
+        <v>6301286.12</v>
       </c>
       <c r="H28" t="n">
         <v>1499694.06</v>
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2719324.85</v>
+        <v>3020706.72</v>
       </c>
       <c r="F30" t="n">
-        <v>1943303.29</v>
+        <v>1946792.06</v>
       </c>
       <c r="G30" t="n">
-        <v>1346017.29</v>
+        <v>1891769.63</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>14088679.2</v>
+        <v>14089679.2</v>
       </c>
       <c r="F33" t="n">
-        <v>10150334.06</v>
+        <v>10218932.06</v>
       </c>
       <c r="G33" t="n">
         <v>9109782.140000001</v>
@@ -1493,19 +1493,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1435771676.37</v>
+        <v>1451036701.01</v>
       </c>
       <c r="F34" t="n">
-        <v>1092570706.34</v>
+        <v>1097251187.75</v>
       </c>
       <c r="G34" t="n">
-        <v>940775249.28</v>
+        <v>945472044.86</v>
       </c>
       <c r="H34" t="n">
-        <v>264060155.38</v>
+        <v>268651744.87</v>
       </c>
       <c r="I34" t="n">
-        <v>245461898.29</v>
+        <v>249998388.71</v>
       </c>
     </row>
     <row r="35">
@@ -1526,19 +1526,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>929143919.91</v>
+        <v>948700388.71</v>
       </c>
       <c r="F35" t="n">
-        <v>564219521.16</v>
+        <v>573559413.83</v>
       </c>
       <c r="G35" t="n">
-        <v>486997835.23</v>
+        <v>504906661.32</v>
       </c>
       <c r="H35" t="n">
-        <v>567287208.3099999</v>
+        <v>571796224.36</v>
       </c>
       <c r="I35" t="n">
-        <v>1012471891.58</v>
+        <v>1021423931.1</v>
       </c>
     </row>
     <row r="36">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>42544902.07</v>
+        <v>43964830.52</v>
       </c>
       <c r="F36" t="n">
-        <v>12997497.91</v>
+        <v>13469389.17</v>
       </c>
       <c r="G36" t="n">
-        <v>10966232.21</v>
+        <v>11318552.03</v>
       </c>
       <c r="H36" t="n">
-        <v>38712818.59</v>
+        <v>39907351.55</v>
       </c>
       <c r="I36" t="n">
-        <v>43751685.05</v>
+        <v>45095365.05</v>
       </c>
     </row>
     <row r="37">
@@ -1592,13 +1592,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>389537.41</v>
+        <v>411364.79</v>
       </c>
       <c r="F37" t="n">
-        <v>325505.69</v>
+        <v>325783.39</v>
       </c>
       <c r="G37" t="n">
-        <v>304680.58</v>
+        <v>304944.95</v>
       </c>
       <c r="H37" t="n">
         <v>1251438.8</v>
@@ -1652,13 +1652,13 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>16375111.89</v>
+        <v>16440845.32</v>
       </c>
       <c r="F39" t="n">
-        <v>10834096.17</v>
+        <v>10948901.45</v>
       </c>
       <c r="G39" t="n">
-        <v>10372955.07</v>
+        <v>10481085.4</v>
       </c>
       <c r="H39" t="n">
         <v>2161550.53</v>
@@ -1685,19 +1685,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>478341486.01</v>
+        <v>487480867.19</v>
       </c>
       <c r="F40" t="n">
-        <v>381087576.67</v>
+        <v>400121836.41</v>
       </c>
       <c r="G40" t="n">
-        <v>342890753.62</v>
+        <v>347218239.44</v>
       </c>
       <c r="H40" t="n">
-        <v>99508258.3</v>
+        <v>99726449.48999999</v>
       </c>
       <c r="I40" t="n">
-        <v>100084193.41</v>
+        <v>100468044.69</v>
       </c>
     </row>
     <row r="41">
@@ -1721,10 +1721,10 @@
         <v>222775.76</v>
       </c>
       <c r="F41" t="n">
-        <v>195711.57</v>
+        <v>222775.76</v>
       </c>
       <c r="G41" t="n">
-        <v>164479.93</v>
+        <v>186763.97</v>
       </c>
       <c r="H41" t="n">
         <v>842769.0699999999</v>
@@ -1781,10 +1781,10 @@
         <v>8163868.5</v>
       </c>
       <c r="F43" t="n">
-        <v>6300081.39</v>
+        <v>6305142.86</v>
       </c>
       <c r="G43" t="n">
-        <v>5457103.79</v>
+        <v>5537225.6</v>
       </c>
       <c r="H43" t="n">
         <v>2576363.8</v>
@@ -1877,13 +1877,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1480644.25</v>
+        <v>1497423.85</v>
       </c>
       <c r="F46" t="n">
-        <v>967430.05</v>
+        <v>1039016.09</v>
       </c>
       <c r="G46" t="n">
-        <v>874286.28</v>
+        <v>928627.59</v>
       </c>
       <c r="H46" t="n">
         <v>178281.27</v>
@@ -1964,16 +1964,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>211040578.99</v>
+        <v>213940137.6</v>
       </c>
       <c r="F49" t="n">
-        <v>146406584.76</v>
+        <v>150326749.26</v>
       </c>
       <c r="G49" t="n">
-        <v>129579455.13</v>
+        <v>130396590.8</v>
       </c>
       <c r="H49" t="n">
-        <v>135331229.29</v>
+        <v>135331656.77</v>
       </c>
       <c r="I49" t="n">
         <v>141000459.38</v>
@@ -2006,10 +2006,10 @@
         <v>14173841.97</v>
       </c>
       <c r="H50" t="n">
-        <v>19810018.83</v>
+        <v>19810614.22</v>
       </c>
       <c r="I50" t="n">
-        <v>21159454.29</v>
+        <v>21159895.87</v>
       </c>
     </row>
     <row r="51">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>94044732.23</v>
+        <v>97629701.23</v>
       </c>
       <c r="F51" t="n">
-        <v>57882497.43</v>
+        <v>59057477.35</v>
       </c>
       <c r="G51" t="n">
-        <v>54816106.12</v>
+        <v>54987294.69</v>
       </c>
       <c r="H51" t="n">
         <v>18617499.53</v>
@@ -2063,13 +2063,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>48405402.56</v>
+        <v>49429749.1</v>
       </c>
       <c r="F52" t="n">
-        <v>21206390.26</v>
+        <v>21468657.17</v>
       </c>
       <c r="G52" t="n">
-        <v>18506076.14</v>
+        <v>18964753.93</v>
       </c>
       <c r="H52" t="n">
         <v>12470050.72</v>
@@ -2123,13 +2123,13 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>142871780.64</v>
+        <v>146396072.66</v>
       </c>
       <c r="F54" t="n">
-        <v>109643004.49</v>
+        <v>111890906.46</v>
       </c>
       <c r="G54" t="n">
-        <v>98165742.48</v>
+        <v>98317974.44</v>
       </c>
       <c r="H54" t="n">
         <v>24490691.01</v>
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>29409821.91</v>
+        <v>29810353.41</v>
       </c>
       <c r="F55" t="n">
-        <v>21545152.47</v>
+        <v>21643916.29</v>
       </c>
       <c r="G55" t="n">
-        <v>20722017.78</v>
+        <v>20985661.34</v>
       </c>
       <c r="H55" t="n">
-        <v>22118707.18</v>
+        <v>22140382.18</v>
       </c>
       <c r="I55" t="n">
-        <v>22868744.96</v>
+        <v>22890160.12</v>
       </c>
     </row>
     <row r="56">
@@ -2189,13 +2189,13 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>44031959.61</v>
+        <v>45995878.1</v>
       </c>
       <c r="F56" t="n">
-        <v>36904199.49</v>
+        <v>39054421.46</v>
       </c>
       <c r="G56" t="n">
-        <v>31023491.7</v>
+        <v>31924889.43</v>
       </c>
       <c r="H56" t="n">
         <v>8627975.140000001</v>
@@ -2222,13 +2222,13 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4266882.26</v>
+        <v>4667411.74</v>
       </c>
       <c r="F57" t="n">
-        <v>3546927.07</v>
+        <v>3960220.12</v>
       </c>
       <c r="G57" t="n">
-        <v>3173108.8</v>
+        <v>3228548.32</v>
       </c>
       <c r="H57" t="n">
         <v>532120.09</v>
@@ -2255,13 +2255,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6719534.81</v>
+        <v>6995627.38</v>
       </c>
       <c r="F58" t="n">
-        <v>4597087.66</v>
+        <v>4879204.46</v>
       </c>
       <c r="G58" t="n">
-        <v>4320007.08</v>
+        <v>4559527.17</v>
       </c>
       <c r="H58" t="n">
         <v>11029049.85</v>
@@ -2288,13 +2288,13 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>14861291.68</v>
+        <v>14985968.97</v>
       </c>
       <c r="F59" t="n">
-        <v>8433425.58</v>
+        <v>8751519.33</v>
       </c>
       <c r="G59" t="n">
-        <v>7571977.46</v>
+        <v>7610772.22</v>
       </c>
       <c r="H59" t="n">
         <v>5237570.34</v>
@@ -2321,13 +2321,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>9262595.25</v>
+        <v>9543644.470000001</v>
       </c>
       <c r="F60" t="n">
-        <v>9017803.58</v>
+        <v>9291129.300000001</v>
       </c>
       <c r="G60" t="n">
-        <v>7916640.25</v>
+        <v>8173772.91</v>
       </c>
       <c r="H60" t="n">
         <v>1332496.42</v>
@@ -2354,13 +2354,13 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>42043986.36</v>
+        <v>47222671.95</v>
       </c>
       <c r="F61" t="n">
-        <v>42043986.36</v>
+        <v>47222671.95</v>
       </c>
       <c r="G61" t="n">
-        <v>42043986.36</v>
+        <v>47222671.95</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -2383,19 +2383,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>236204307.71</v>
+        <v>238917109.87</v>
       </c>
       <c r="F62" t="n">
-        <v>184849969.63</v>
+        <v>193375069.51</v>
       </c>
       <c r="G62" t="n">
-        <v>170020318.08</v>
+        <v>179475084.47</v>
       </c>
       <c r="H62" t="n">
-        <v>198983832.99</v>
+        <v>199055061.08</v>
       </c>
       <c r="I62" t="n">
-        <v>194272748.12</v>
+        <v>194341491.84</v>
       </c>
     </row>
     <row r="63">
@@ -2416,19 +2416,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>67828383.36</v>
+        <v>66845383.36</v>
       </c>
       <c r="F63" t="n">
-        <v>48384727.31</v>
+        <v>53539938.46</v>
       </c>
       <c r="G63" t="n">
-        <v>43905078.36</v>
+        <v>43974097.76</v>
       </c>
       <c r="H63" t="n">
-        <v>35392114.99</v>
+        <v>35392441.77</v>
       </c>
       <c r="I63" t="n">
-        <v>53898519.67</v>
+        <v>53934542.42</v>
       </c>
     </row>
     <row r="64">
@@ -2449,13 +2449,13 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>11541979.66</v>
+        <v>11607890.08</v>
       </c>
       <c r="F64" t="n">
         <v>8064558.63</v>
       </c>
       <c r="G64" t="n">
-        <v>6925082.61</v>
+        <v>7591360.75</v>
       </c>
       <c r="H64" t="n">
         <v>1960878.57</v>
@@ -2485,10 +2485,10 @@
         <v>584746.91</v>
       </c>
       <c r="F65" t="n">
-        <v>468155.48</v>
+        <v>561739.67</v>
       </c>
       <c r="G65" t="n">
-        <v>405609.52</v>
+        <v>484972.44</v>
       </c>
       <c r="H65" t="n">
         <v>34744.58</v>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1470240.61</v>
+        <v>1474364.46</v>
       </c>
       <c r="F67" t="n">
         <v>1193299.64</v>
@@ -2551,10 +2551,10 @@
         <v>1103997.51</v>
       </c>
       <c r="H67" t="n">
-        <v>94459.97</v>
+        <v>94595.71000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>93457.72</v>
+        <v>93586.94</v>
       </c>
     </row>
     <row r="68">
@@ -2575,19 +2575,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>234786515.26</v>
+        <v>246468987.84</v>
       </c>
       <c r="F68" t="n">
-        <v>171889919.57</v>
+        <v>187529645.68</v>
       </c>
       <c r="G68" t="n">
-        <v>151772993.4</v>
+        <v>153213333.12</v>
       </c>
       <c r="H68" t="n">
-        <v>49463492.27</v>
+        <v>49474619.75</v>
       </c>
       <c r="I68" t="n">
-        <v>48253127.95</v>
+        <v>48319062.06</v>
       </c>
     </row>
     <row r="69">
@@ -2608,19 +2608,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>260710928.02</v>
+        <v>270265210.42</v>
       </c>
       <c r="F69" t="n">
-        <v>194028271.69</v>
+        <v>196511634.68</v>
       </c>
       <c r="G69" t="n">
-        <v>166810496.62</v>
+        <v>168933198.89</v>
       </c>
       <c r="H69" t="n">
-        <v>88100410.09</v>
+        <v>88100522.73999999</v>
       </c>
       <c r="I69" t="n">
-        <v>84956671.15000001</v>
+        <v>84956779.47</v>
       </c>
     </row>
     <row r="70">
@@ -2641,19 +2641,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>485810309.21</v>
+        <v>494652449.31</v>
       </c>
       <c r="F70" t="n">
-        <v>303996284.61</v>
+        <v>312050998.41</v>
       </c>
       <c r="G70" t="n">
-        <v>267816295.82</v>
+        <v>277120152.85</v>
       </c>
       <c r="H70" t="n">
-        <v>235557840.68</v>
+        <v>235618798.54</v>
       </c>
       <c r="I70" t="n">
-        <v>205152026.49</v>
+        <v>205259183.86</v>
       </c>
     </row>
     <row r="71">
@@ -2677,10 +2677,10 @@
         <v>1086537.57</v>
       </c>
       <c r="F71" t="n">
-        <v>986783.6800000001</v>
+        <v>1063747.56</v>
       </c>
       <c r="G71" t="n">
-        <v>880176.9300000001</v>
+        <v>924442.6899999999</v>
       </c>
       <c r="H71" t="n">
         <v>225243.01</v>
@@ -2707,13 +2707,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>58978647.59</v>
+        <v>59110548.59</v>
       </c>
       <c r="F72" t="n">
-        <v>38585801.96</v>
+        <v>38630645.31</v>
       </c>
       <c r="G72" t="n">
-        <v>37118035.4</v>
+        <v>37160449.89</v>
       </c>
       <c r="H72" t="n">
         <v>19489131.64</v>
@@ -2740,13 +2740,13 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1732099.9</v>
+        <v>1784536.37</v>
       </c>
       <c r="F73" t="n">
-        <v>1398181.53</v>
+        <v>1557406.41</v>
       </c>
       <c r="G73" t="n">
-        <v>1233215.85</v>
+        <v>1335480.21</v>
       </c>
       <c r="H73" t="n">
         <v>34378.25</v>
@@ -2773,19 +2773,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>79403938.59</v>
+        <v>91161042.12</v>
       </c>
       <c r="F74" t="n">
-        <v>64175278.12</v>
+        <v>65227308.63</v>
       </c>
       <c r="G74" t="n">
-        <v>60217584.82</v>
+        <v>61234742.26</v>
       </c>
       <c r="H74" t="n">
-        <v>66007855.09</v>
+        <v>66745461.28</v>
       </c>
       <c r="I74" t="n">
-        <v>62689623.1</v>
+        <v>62742403.58</v>
       </c>
     </row>
     <row r="75">
@@ -2806,13 +2806,13 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>19256664.18</v>
+        <v>19270546.18</v>
       </c>
       <c r="F75" t="n">
-        <v>15178006.27</v>
+        <v>16266161</v>
       </c>
       <c r="G75" t="n">
-        <v>12006129.05</v>
+        <v>13485858.86</v>
       </c>
       <c r="H75" t="n">
         <v>674995.91</v>
@@ -2839,16 +2839,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>242899915.51</v>
+        <v>242952007.51</v>
       </c>
       <c r="F76" t="n">
-        <v>11725453.81</v>
+        <v>13179804.85</v>
       </c>
       <c r="G76" t="n">
-        <v>10427477.65</v>
+        <v>11510927.08</v>
       </c>
       <c r="H76" t="n">
-        <v>50036034.12</v>
+        <v>50585699.32</v>
       </c>
       <c r="I76" t="n">
         <v>47319399.62</v>
@@ -2872,19 +2872,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>26313213.94</v>
+        <v>26607344.26</v>
       </c>
       <c r="F77" t="n">
-        <v>21575294.77</v>
+        <v>22085520.18</v>
       </c>
       <c r="G77" t="n">
-        <v>17870272.12</v>
+        <v>19744337.53</v>
       </c>
       <c r="H77" t="n">
-        <v>18126905.4</v>
+        <v>18154376.27</v>
       </c>
       <c r="I77" t="n">
-        <v>29279133.49</v>
+        <v>29303994.63</v>
       </c>
     </row>
     <row r="78">
@@ -2905,19 +2905,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>953992229.74</v>
+        <v>970087628.3099999</v>
       </c>
       <c r="F78" t="n">
-        <v>723891311.2</v>
+        <v>739096255.62</v>
       </c>
       <c r="G78" t="n">
-        <v>698450457.41</v>
+        <v>713367442.08</v>
       </c>
       <c r="H78" t="n">
-        <v>155884404.2</v>
+        <v>157440192.63</v>
       </c>
       <c r="I78" t="n">
-        <v>351009889.12</v>
+        <v>352178826.45</v>
       </c>
     </row>
     <row r="79">
@@ -2938,19 +2938,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>182912408.42</v>
+        <v>189602554.73</v>
       </c>
       <c r="F79" t="n">
-        <v>134834701.28</v>
+        <v>138321317.18</v>
       </c>
       <c r="G79" t="n">
-        <v>107583959.85</v>
+        <v>107916254.16</v>
       </c>
       <c r="H79" t="n">
         <v>62673101.03</v>
       </c>
       <c r="I79" t="n">
-        <v>66670976.86</v>
+        <v>66788140.89</v>
       </c>
     </row>
     <row r="80">
@@ -2971,13 +2971,13 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>30538470.74</v>
+        <v>30864031.14</v>
       </c>
       <c r="F80" t="n">
-        <v>26673915.73</v>
+        <v>27066019.4</v>
       </c>
       <c r="G80" t="n">
-        <v>24684840.67</v>
+        <v>24770980.49</v>
       </c>
       <c r="H80" t="n">
         <v>4983225.57</v>
@@ -3004,16 +3004,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>53609808.85</v>
+        <v>53720447.55</v>
       </c>
       <c r="F81" t="n">
-        <v>29669424.88</v>
+        <v>30520466.38</v>
       </c>
       <c r="G81" t="n">
-        <v>26613915.68</v>
+        <v>26978325.24</v>
       </c>
       <c r="H81" t="n">
-        <v>92783753.01000001</v>
+        <v>93035965.29000001</v>
       </c>
       <c r="I81" t="n">
         <v>149841879.2</v>
@@ -3037,19 +3037,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>606278842.4400001</v>
+        <v>610001632.2</v>
       </c>
       <c r="F82" t="n">
-        <v>446204838.77</v>
+        <v>451888200.92</v>
       </c>
       <c r="G82" t="n">
-        <v>422722271.24</v>
+        <v>428692401.42</v>
       </c>
       <c r="H82" t="n">
-        <v>144895064.91</v>
+        <v>145105621.93</v>
       </c>
       <c r="I82" t="n">
-        <v>152004702.77</v>
+        <v>152617812.4</v>
       </c>
     </row>
     <row r="83">
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>31512844.84</v>
+        <v>31743384.51</v>
       </c>
       <c r="F83" t="n">
-        <v>26993582.24</v>
+        <v>27291253.35</v>
       </c>
       <c r="G83" t="n">
-        <v>20987360.64</v>
+        <v>23579319.56</v>
       </c>
       <c r="H83" t="n">
         <v>4788552.39</v>
@@ -3103,19 +3103,19 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>284016956.71</v>
+        <v>283562979.71</v>
       </c>
       <c r="F84" t="n">
-        <v>207719080.21</v>
+        <v>216285129.65</v>
       </c>
       <c r="G84" t="n">
-        <v>186399379.79</v>
+        <v>188584148.63</v>
       </c>
       <c r="H84" t="n">
         <v>74964907.94</v>
       </c>
       <c r="I84" t="n">
-        <v>100438151.39</v>
+        <v>99677843.55</v>
       </c>
     </row>
     <row r="85">
@@ -3136,19 +3136,19 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>94483925.47</v>
+        <v>95543759.13</v>
       </c>
       <c r="F85" t="n">
-        <v>69372102.87</v>
+        <v>70049664.89</v>
       </c>
       <c r="G85" t="n">
-        <v>58646143.53</v>
+        <v>59149824.92</v>
       </c>
       <c r="H85" t="n">
-        <v>34226175.48</v>
+        <v>34371578.38</v>
       </c>
       <c r="I85" t="n">
-        <v>29952557.14</v>
+        <v>30087345.63</v>
       </c>
     </row>
     <row r="86">
@@ -3169,13 +3169,13 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>9992152.27</v>
+        <v>10099744.05</v>
       </c>
       <c r="F86" t="n">
-        <v>8249961.66</v>
+        <v>8427815.470000001</v>
       </c>
       <c r="G86" t="n">
-        <v>7420904.84</v>
+        <v>7504646.16</v>
       </c>
       <c r="H86" t="n">
         <v>5342633.4</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5543851.35</v>
+        <v>5662062.43</v>
       </c>
       <c r="F87" t="n">
-        <v>4292556.54</v>
+        <v>4760884.23</v>
       </c>
       <c r="G87" t="n">
         <v>3036744.6</v>
@@ -3235,19 +3235,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>66762770.06</v>
+        <v>68528819.48999999</v>
       </c>
       <c r="F88" t="n">
-        <v>48062788.92</v>
+        <v>48467299.88</v>
       </c>
       <c r="G88" t="n">
-        <v>42846124.83</v>
+        <v>43141302.15</v>
       </c>
       <c r="H88" t="n">
-        <v>20790290.67</v>
+        <v>20790468.79</v>
       </c>
       <c r="I88" t="n">
-        <v>19991976.69</v>
+        <v>19992125.98</v>
       </c>
     </row>
     <row r="89">
@@ -3268,19 +3268,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>57160466.52</v>
+        <v>57419511.15</v>
       </c>
       <c r="F89" t="n">
-        <v>38069320.72</v>
+        <v>41113437.23</v>
       </c>
       <c r="G89" t="n">
-        <v>34126736.11</v>
+        <v>36756683.13</v>
       </c>
       <c r="H89" t="n">
-        <v>25670879.72</v>
+        <v>25671551.83</v>
       </c>
       <c r="I89" t="n">
-        <v>23665823.26</v>
+        <v>23666371.42</v>
       </c>
     </row>
     <row r="90">
@@ -3301,13 +3301,13 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2321177.78</v>
+        <v>2351482.68</v>
       </c>
       <c r="F90" t="n">
-        <v>2069207.73</v>
+        <v>2086137.58</v>
       </c>
       <c r="G90" t="n">
-        <v>1815836.86</v>
+        <v>1832442.34</v>
       </c>
       <c r="H90" t="n">
         <v>294468.9</v>

--- a/upload/orgao2026.xlsx
+++ b/upload/orgao2026.xlsx
@@ -493,19 +493,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>22915657.51</v>
+        <v>22964754.83</v>
       </c>
       <c r="F2" t="n">
-        <v>16496274.91</v>
+        <v>17796454.15</v>
       </c>
       <c r="G2" t="n">
-        <v>14899520.38</v>
+        <v>15711605.91</v>
       </c>
       <c r="H2" t="n">
-        <v>2727880.95</v>
+        <v>2739450.58</v>
       </c>
       <c r="I2" t="n">
-        <v>216945133.94</v>
+        <v>216945307.51</v>
       </c>
     </row>
     <row r="3">
@@ -526,13 +526,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1986291.21</v>
+        <v>1988237.21</v>
       </c>
       <c r="F3" t="n">
-        <v>1601658.7</v>
+        <v>1823331.67</v>
       </c>
       <c r="G3" t="n">
-        <v>1379790.37</v>
+        <v>1568745.9</v>
       </c>
       <c r="H3" t="n">
         <v>60903.67</v>
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>178948067.63</v>
+        <v>181123157.12</v>
       </c>
       <c r="F4" t="n">
-        <v>110496155.24</v>
+        <v>123062207.36</v>
       </c>
       <c r="G4" t="n">
-        <v>99521480.12</v>
+        <v>101966314.82</v>
       </c>
       <c r="H4" t="n">
-        <v>35391637.95</v>
+        <v>35437295.33</v>
       </c>
       <c r="I4" t="n">
         <v>32828534.51</v>
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2861063.88</v>
+        <v>2860947.26</v>
       </c>
       <c r="F5" t="n">
-        <v>1762924.14</v>
+        <v>1782779.57</v>
       </c>
       <c r="G5" t="n">
-        <v>1523539.95</v>
+        <v>1536922.89</v>
       </c>
       <c r="H5" t="n">
         <v>706301.5699999999</v>
@@ -625,19 +625,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2499067.64</v>
+        <v>2534743.44</v>
       </c>
       <c r="F6" t="n">
-        <v>1455598.88</v>
+        <v>1525006.73</v>
       </c>
       <c r="G6" t="n">
-        <v>1366243.16</v>
+        <v>1435208.41</v>
       </c>
       <c r="H6" t="n">
-        <v>154717.57</v>
+        <v>155417.57</v>
       </c>
       <c r="I6" t="n">
-        <v>148604.18</v>
+        <v>150004.18</v>
       </c>
     </row>
     <row r="7">
@@ -664,7 +664,7 @@
         <v>19790080.52</v>
       </c>
       <c r="G7" t="n">
-        <v>17519267.59</v>
+        <v>17801865.2</v>
       </c>
       <c r="H7" t="n">
         <v>2353030.07</v>
@@ -691,19 +691,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>79863957.14</v>
+        <v>80080190.81</v>
       </c>
       <c r="F8" t="n">
-        <v>33889776.63</v>
+        <v>34674047.28</v>
       </c>
       <c r="G8" t="n">
-        <v>29369112.68</v>
+        <v>29956635.23</v>
       </c>
       <c r="H8" t="n">
-        <v>51118822.19</v>
+        <v>51984004.75</v>
       </c>
       <c r="I8" t="n">
-        <v>49029933.96</v>
+        <v>49956435.51</v>
       </c>
     </row>
     <row r="9">
@@ -727,10 +727,10 @@
         <v>3484649.64</v>
       </c>
       <c r="F9" t="n">
-        <v>2700019.98</v>
+        <v>2892131.78</v>
       </c>
       <c r="G9" t="n">
-        <v>2602959.85</v>
+        <v>2607121.32</v>
       </c>
       <c r="H9" t="n">
         <v>1345976.77</v>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>83451344.81</v>
+        <v>84028469.56999999</v>
       </c>
       <c r="F10" t="n">
-        <v>76749035.73999999</v>
+        <v>79689833.90000001</v>
       </c>
       <c r="G10" t="n">
-        <v>64331542.04</v>
+        <v>66929218.67</v>
       </c>
       <c r="H10" t="n">
         <v>14925708.98</v>
@@ -790,19 +790,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1621116303.32</v>
+        <v>1622787372.01</v>
       </c>
       <c r="F11" t="n">
-        <v>834816709.8</v>
+        <v>843533995.0700001</v>
       </c>
       <c r="G11" t="n">
-        <v>814730941.02</v>
+        <v>819480688.91</v>
       </c>
       <c r="H11" t="n">
-        <v>338223224.55</v>
+        <v>338841681.47</v>
       </c>
       <c r="I11" t="n">
-        <v>342813777.57</v>
+        <v>346228341.19</v>
       </c>
     </row>
     <row r="12">
@@ -823,13 +823,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>34227344.15</v>
+        <v>32788395.03</v>
       </c>
       <c r="F12" t="n">
-        <v>10340289.26</v>
+        <v>16913469.15</v>
       </c>
       <c r="G12" t="n">
-        <v>9542932.08</v>
+        <v>12696575.19</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8668649.49</v>
+        <v>8686779.15</v>
       </c>
       <c r="F19" t="n">
-        <v>4402544.98</v>
+        <v>4437938.21</v>
       </c>
       <c r="G19" t="n">
-        <v>4030056.44</v>
+        <v>4065982.23</v>
       </c>
       <c r="H19" t="n">
         <v>1040158.72</v>
@@ -1064,10 +1064,10 @@
         <v>358206</v>
       </c>
       <c r="F20" t="n">
-        <v>223427.58</v>
+        <v>243531.59</v>
       </c>
       <c r="G20" t="n">
-        <v>211696.11</v>
+        <v>230061.11</v>
       </c>
       <c r="H20" t="n">
         <v>30324.78</v>
@@ -1094,13 +1094,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1004317.92</v>
+        <v>1009317.92</v>
       </c>
       <c r="F21" t="n">
-        <v>838104.04</v>
+        <v>850442.89</v>
       </c>
       <c r="G21" t="n">
-        <v>693062.3</v>
+        <v>705315.21</v>
       </c>
       <c r="H21" t="n">
         <v>97349.38</v>
@@ -1127,19 +1127,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>19017448.76</v>
+        <v>19519429.76</v>
       </c>
       <c r="F22" t="n">
-        <v>16485291.12</v>
+        <v>16588828.63</v>
       </c>
       <c r="G22" t="n">
-        <v>14689413.44</v>
+        <v>14694032.82</v>
       </c>
       <c r="H22" t="n">
-        <v>4345882.84</v>
+        <v>4348132.84</v>
       </c>
       <c r="I22" t="n">
-        <v>7074260.62</v>
+        <v>7649550.61</v>
       </c>
     </row>
     <row r="23">
@@ -1160,13 +1160,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>8970870.439999999</v>
+        <v>9939388.289999999</v>
       </c>
       <c r="F23" t="n">
-        <v>8009583.65</v>
+        <v>8009614.81</v>
       </c>
       <c r="G23" t="n">
-        <v>7062983.28</v>
+        <v>7075379.22</v>
       </c>
       <c r="H23" t="n">
         <v>1741057.76</v>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>11280695.13</v>
+        <v>11752364.48</v>
       </c>
       <c r="F26" t="n">
-        <v>4407081.74</v>
+        <v>4613249.44</v>
       </c>
       <c r="G26" t="n">
-        <v>4357523.1</v>
+        <v>4379359.54</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -1284,16 +1284,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>9829781.16</v>
+        <v>10326294.24</v>
       </c>
       <c r="F27" t="n">
-        <v>9424323.33</v>
+        <v>10005422.98</v>
       </c>
       <c r="G27" t="n">
-        <v>7650353.71</v>
+        <v>7786999.03</v>
       </c>
       <c r="H27" t="n">
-        <v>1102595.36</v>
+        <v>1102594.36</v>
       </c>
       <c r="I27" t="n">
         <v>1012619.95</v>
@@ -1317,19 +1317,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>9063969.41</v>
+        <v>9141817.49</v>
       </c>
       <c r="F28" t="n">
-        <v>7103215.07</v>
+        <v>7203499.54</v>
       </c>
       <c r="G28" t="n">
-        <v>6301286.12</v>
+        <v>6323518.64</v>
       </c>
       <c r="H28" t="n">
         <v>1499694.06</v>
       </c>
       <c r="I28" t="n">
-        <v>1993885.76</v>
+        <v>2008315.56</v>
       </c>
     </row>
     <row r="29">
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3020706.72</v>
+        <v>3850872.47</v>
       </c>
       <c r="F30" t="n">
-        <v>1946792.06</v>
+        <v>1987053.07</v>
       </c>
       <c r="G30" t="n">
-        <v>1891769.63</v>
+        <v>1894368.53</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -1460,13 +1460,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>14089679.2</v>
+        <v>14205719.8</v>
       </c>
       <c r="F33" t="n">
-        <v>10218932.06</v>
+        <v>10406370.48</v>
       </c>
       <c r="G33" t="n">
-        <v>9109782.140000001</v>
+        <v>9178462.51</v>
       </c>
       <c r="H33" t="n">
         <v>33176516.48</v>
@@ -1493,13 +1493,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1451036701.01</v>
+        <v>1488604375.03</v>
       </c>
       <c r="F34" t="n">
-        <v>1097251187.75</v>
+        <v>1119826614.67</v>
       </c>
       <c r="G34" t="n">
-        <v>945472044.86</v>
+        <v>966181211.83</v>
       </c>
       <c r="H34" t="n">
         <v>268651744.87</v>
@@ -1526,19 +1526,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>948700388.71</v>
+        <v>965772356.1799999</v>
       </c>
       <c r="F35" t="n">
-        <v>573559413.83</v>
+        <v>592416074.5599999</v>
       </c>
       <c r="G35" t="n">
-        <v>504906661.32</v>
+        <v>526924979.41</v>
       </c>
       <c r="H35" t="n">
-        <v>571796224.36</v>
+        <v>575919628.8200001</v>
       </c>
       <c r="I35" t="n">
-        <v>1021423931.1</v>
+        <v>1027604802.87</v>
       </c>
     </row>
     <row r="36">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>43964830.52</v>
+        <v>45010853.56</v>
       </c>
       <c r="F36" t="n">
-        <v>13469389.17</v>
+        <v>14099885.53</v>
       </c>
       <c r="G36" t="n">
-        <v>11318552.03</v>
+        <v>12641629.3</v>
       </c>
       <c r="H36" t="n">
-        <v>39907351.55</v>
+        <v>44402351.55</v>
       </c>
       <c r="I36" t="n">
-        <v>45095365.05</v>
+        <v>45305846.54</v>
       </c>
     </row>
     <row r="37">
@@ -1595,10 +1595,10 @@
         <v>411364.79</v>
       </c>
       <c r="F37" t="n">
-        <v>325783.39</v>
+        <v>332205.11</v>
       </c>
       <c r="G37" t="n">
-        <v>304944.95</v>
+        <v>311058.43</v>
       </c>
       <c r="H37" t="n">
         <v>1251438.8</v>
@@ -1652,13 +1652,13 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>16440845.32</v>
+        <v>18768517.53</v>
       </c>
       <c r="F39" t="n">
-        <v>10948901.45</v>
+        <v>11089972.48</v>
       </c>
       <c r="G39" t="n">
-        <v>10481085.4</v>
+        <v>10617739.62</v>
       </c>
       <c r="H39" t="n">
         <v>2161550.53</v>
@@ -1685,19 +1685,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>487480867.19</v>
+        <v>509125527.9</v>
       </c>
       <c r="F40" t="n">
-        <v>400121836.41</v>
+        <v>416174404.29</v>
       </c>
       <c r="G40" t="n">
-        <v>347218239.44</v>
+        <v>366024577.84</v>
       </c>
       <c r="H40" t="n">
-        <v>99726449.48999999</v>
+        <v>99813715.72</v>
       </c>
       <c r="I40" t="n">
-        <v>100468044.69</v>
+        <v>100613543.18</v>
       </c>
     </row>
     <row r="41">
@@ -1778,19 +1778,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>8163868.5</v>
+        <v>8325868.29</v>
       </c>
       <c r="F43" t="n">
-        <v>6305142.86</v>
+        <v>7157428</v>
       </c>
       <c r="G43" t="n">
-        <v>5537225.6</v>
+        <v>6075686.75</v>
       </c>
       <c r="H43" t="n">
         <v>2576363.8</v>
       </c>
       <c r="I43" t="n">
-        <v>2281047.66</v>
+        <v>2406586.33</v>
       </c>
     </row>
     <row r="44">
@@ -1844,13 +1844,13 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>583177905.95</v>
+        <v>595515563.95</v>
       </c>
       <c r="F45" t="n">
-        <v>235304145.23</v>
+        <v>246638164.48</v>
       </c>
       <c r="G45" t="n">
-        <v>213416651.16</v>
+        <v>216615430.98</v>
       </c>
       <c r="H45" t="n">
         <v>38776739.66</v>
@@ -1877,13 +1877,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1497423.85</v>
+        <v>1732263.47</v>
       </c>
       <c r="F46" t="n">
-        <v>1039016.09</v>
+        <v>1052946.96</v>
       </c>
       <c r="G46" t="n">
-        <v>928627.59</v>
+        <v>954583.67</v>
       </c>
       <c r="H46" t="n">
         <v>178281.27</v>
@@ -1964,16 +1964,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>213940137.6</v>
+        <v>216122326.56</v>
       </c>
       <c r="F49" t="n">
-        <v>150326749.26</v>
+        <v>151627268.83</v>
       </c>
       <c r="G49" t="n">
-        <v>130396590.8</v>
+        <v>132375564.95</v>
       </c>
       <c r="H49" t="n">
-        <v>135331656.77</v>
+        <v>136515156.77</v>
       </c>
       <c r="I49" t="n">
         <v>141000459.38</v>
@@ -2000,16 +2000,16 @@
         <v>15780207.31</v>
       </c>
       <c r="F50" t="n">
-        <v>14607689.09</v>
+        <v>15045689.09</v>
       </c>
       <c r="G50" t="n">
-        <v>14173841.97</v>
+        <v>14437836.75</v>
       </c>
       <c r="H50" t="n">
-        <v>19810614.22</v>
+        <v>19814010.18</v>
       </c>
       <c r="I50" t="n">
-        <v>21159895.87</v>
+        <v>21160337.38</v>
       </c>
     </row>
     <row r="51">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>97629701.23</v>
+        <v>105171538.95</v>
       </c>
       <c r="F51" t="n">
-        <v>59057477.35</v>
+        <v>61200749.74</v>
       </c>
       <c r="G51" t="n">
-        <v>54987294.69</v>
+        <v>56948967.43</v>
       </c>
       <c r="H51" t="n">
         <v>18617499.53</v>
@@ -2063,13 +2063,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>49429749.1</v>
+        <v>49837193.49</v>
       </c>
       <c r="F52" t="n">
-        <v>21468657.17</v>
+        <v>22255848.04</v>
       </c>
       <c r="G52" t="n">
-        <v>18964753.93</v>
+        <v>19172013</v>
       </c>
       <c r="H52" t="n">
         <v>12470050.72</v>
@@ -2123,16 +2123,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>146396072.66</v>
+        <v>145271780.36</v>
       </c>
       <c r="F54" t="n">
-        <v>111890906.46</v>
+        <v>114467766.22</v>
       </c>
       <c r="G54" t="n">
-        <v>98317974.44</v>
+        <v>102278124.83</v>
       </c>
       <c r="H54" t="n">
-        <v>24490691.01</v>
+        <v>24493382.91</v>
       </c>
       <c r="I54" t="n">
         <v>27303259.79</v>
@@ -2159,10 +2159,10 @@
         <v>29810353.41</v>
       </c>
       <c r="F55" t="n">
-        <v>21643916.29</v>
+        <v>24100045.8</v>
       </c>
       <c r="G55" t="n">
-        <v>20985661.34</v>
+        <v>23417539.66</v>
       </c>
       <c r="H55" t="n">
         <v>22140382.18</v>
@@ -2189,16 +2189,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>45995878.1</v>
+        <v>46455276.75</v>
       </c>
       <c r="F56" t="n">
-        <v>39054421.46</v>
+        <v>41014666.72</v>
       </c>
       <c r="G56" t="n">
-        <v>31924889.43</v>
+        <v>32796558.59</v>
       </c>
       <c r="H56" t="n">
-        <v>8627975.140000001</v>
+        <v>8629501.859999999</v>
       </c>
       <c r="I56" t="n">
         <v>8371087.11</v>
@@ -2222,13 +2222,13 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4667411.74</v>
+        <v>4717218.3</v>
       </c>
       <c r="F57" t="n">
-        <v>3960220.12</v>
+        <v>4003129.8</v>
       </c>
       <c r="G57" t="n">
-        <v>3228548.32</v>
+        <v>3569130.7</v>
       </c>
       <c r="H57" t="n">
         <v>532120.09</v>
@@ -2255,19 +2255,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6995627.38</v>
+        <v>7022646.38</v>
       </c>
       <c r="F58" t="n">
-        <v>4879204.46</v>
+        <v>4922637.29</v>
       </c>
       <c r="G58" t="n">
-        <v>4559527.17</v>
+        <v>4601239.52</v>
       </c>
       <c r="H58" t="n">
         <v>11029049.85</v>
       </c>
       <c r="I58" t="n">
-        <v>17962923.73</v>
+        <v>18832657.4</v>
       </c>
     </row>
     <row r="59">
@@ -2288,13 +2288,13 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>14985968.97</v>
+        <v>14202817.76</v>
       </c>
       <c r="F59" t="n">
-        <v>8751519.33</v>
+        <v>9076000.09</v>
       </c>
       <c r="G59" t="n">
-        <v>7610772.22</v>
+        <v>8399636.689999999</v>
       </c>
       <c r="H59" t="n">
         <v>5237570.34</v>
@@ -2321,13 +2321,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>9543644.470000001</v>
+        <v>10895862.68</v>
       </c>
       <c r="F60" t="n">
-        <v>9291129.300000001</v>
+        <v>10149198.57</v>
       </c>
       <c r="G60" t="n">
-        <v>8173772.91</v>
+        <v>8999066.859999999</v>
       </c>
       <c r="H60" t="n">
         <v>1332496.42</v>
@@ -2383,19 +2383,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>238917109.87</v>
+        <v>241270000.98</v>
       </c>
       <c r="F62" t="n">
-        <v>193375069.51</v>
+        <v>199826895.97</v>
       </c>
       <c r="G62" t="n">
-        <v>179475084.47</v>
+        <v>184757680.36</v>
       </c>
       <c r="H62" t="n">
-        <v>199055061.08</v>
+        <v>199082035.29</v>
       </c>
       <c r="I62" t="n">
-        <v>194341491.84</v>
+        <v>194368466.05</v>
       </c>
     </row>
     <row r="63">
@@ -2416,19 +2416,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>66845383.36</v>
+        <v>67980365.77</v>
       </c>
       <c r="F63" t="n">
-        <v>53539938.46</v>
+        <v>53728205.92</v>
       </c>
       <c r="G63" t="n">
-        <v>43974097.76</v>
+        <v>48626257.12</v>
       </c>
       <c r="H63" t="n">
         <v>35392441.77</v>
       </c>
       <c r="I63" t="n">
-        <v>53934542.42</v>
+        <v>53948333.28</v>
       </c>
     </row>
     <row r="64">
@@ -2449,13 +2449,13 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>11607890.08</v>
+        <v>11619061.16</v>
       </c>
       <c r="F64" t="n">
-        <v>8064558.63</v>
+        <v>8338706.58</v>
       </c>
       <c r="G64" t="n">
-        <v>7591360.75</v>
+        <v>7809048.74</v>
       </c>
       <c r="H64" t="n">
         <v>1960878.57</v>
@@ -2482,13 +2482,13 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>584746.91</v>
+        <v>626618.0699999999</v>
       </c>
       <c r="F65" t="n">
-        <v>561739.67</v>
+        <v>571577.77</v>
       </c>
       <c r="G65" t="n">
-        <v>484972.44</v>
+        <v>494572.91</v>
       </c>
       <c r="H65" t="n">
         <v>34744.58</v>
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1474364.46</v>
+        <v>1467968.73</v>
       </c>
       <c r="F67" t="n">
-        <v>1193299.64</v>
+        <v>1228701.65</v>
       </c>
       <c r="G67" t="n">
-        <v>1103997.51</v>
+        <v>1139013.87</v>
       </c>
       <c r="H67" t="n">
         <v>94595.71000000001</v>
@@ -2575,19 +2575,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>246468987.84</v>
+        <v>248019910.24</v>
       </c>
       <c r="F68" t="n">
-        <v>187529645.68</v>
+        <v>191229727.31</v>
       </c>
       <c r="G68" t="n">
-        <v>153213333.12</v>
+        <v>174521870.25</v>
       </c>
       <c r="H68" t="n">
-        <v>49474619.75</v>
+        <v>53256400.68</v>
       </c>
       <c r="I68" t="n">
-        <v>48319062.06</v>
+        <v>60344287.52</v>
       </c>
     </row>
     <row r="69">
@@ -2608,19 +2608,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>270265210.42</v>
+        <v>274678795.42</v>
       </c>
       <c r="F69" t="n">
-        <v>196511634.68</v>
+        <v>199868797.86</v>
       </c>
       <c r="G69" t="n">
-        <v>168933198.89</v>
+        <v>172892523.36</v>
       </c>
       <c r="H69" t="n">
-        <v>88100522.73999999</v>
+        <v>89356852.52</v>
       </c>
       <c r="I69" t="n">
-        <v>84956779.47</v>
+        <v>85236865.42</v>
       </c>
     </row>
     <row r="70">
@@ -2641,19 +2641,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>494652449.31</v>
+        <v>506420728.52</v>
       </c>
       <c r="F70" t="n">
-        <v>312050998.41</v>
+        <v>347095331.01</v>
       </c>
       <c r="G70" t="n">
-        <v>277120152.85</v>
+        <v>292653309.75</v>
       </c>
       <c r="H70" t="n">
-        <v>235618798.54</v>
+        <v>244247142.58</v>
       </c>
       <c r="I70" t="n">
-        <v>205259183.86</v>
+        <v>206328788.11</v>
       </c>
     </row>
     <row r="71">
@@ -2674,13 +2674,13 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1086537.57</v>
+        <v>1091554.25</v>
       </c>
       <c r="F71" t="n">
-        <v>1063747.56</v>
+        <v>1063776.19</v>
       </c>
       <c r="G71" t="n">
-        <v>924442.6899999999</v>
+        <v>952134.78</v>
       </c>
       <c r="H71" t="n">
         <v>225243.01</v>
@@ -2707,19 +2707,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>59110548.59</v>
+        <v>58821482.15</v>
       </c>
       <c r="F72" t="n">
-        <v>38630645.31</v>
+        <v>38851490.85</v>
       </c>
       <c r="G72" t="n">
-        <v>37160449.89</v>
+        <v>37375031.76</v>
       </c>
       <c r="H72" t="n">
-        <v>19489131.64</v>
+        <v>19576645.24</v>
       </c>
       <c r="I72" t="n">
-        <v>26030133.64</v>
+        <v>26116597.08</v>
       </c>
     </row>
     <row r="73">
@@ -2740,13 +2740,13 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1784536.37</v>
+        <v>1785466.95</v>
       </c>
       <c r="F73" t="n">
-        <v>1557406.41</v>
+        <v>1575389.44</v>
       </c>
       <c r="G73" t="n">
-        <v>1335480.21</v>
+        <v>1366656.76</v>
       </c>
       <c r="H73" t="n">
         <v>34378.25</v>
@@ -2773,19 +2773,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>91161042.12</v>
+        <v>108711330.48</v>
       </c>
       <c r="F74" t="n">
-        <v>65227308.63</v>
+        <v>66326632.83</v>
       </c>
       <c r="G74" t="n">
-        <v>61234742.26</v>
+        <v>62062183.61</v>
       </c>
       <c r="H74" t="n">
-        <v>66745461.28</v>
+        <v>66894090.28</v>
       </c>
       <c r="I74" t="n">
-        <v>62742403.58</v>
+        <v>63485193.53</v>
       </c>
     </row>
     <row r="75">
@@ -2806,13 +2806,13 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>19270546.18</v>
+        <v>19297933.07</v>
       </c>
       <c r="F75" t="n">
-        <v>16266161</v>
+        <v>16337873.19</v>
       </c>
       <c r="G75" t="n">
-        <v>13485858.86</v>
+        <v>13912090.11</v>
       </c>
       <c r="H75" t="n">
         <v>674995.91</v>
@@ -2839,19 +2839,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>242952007.51</v>
+        <v>243275271.49</v>
       </c>
       <c r="F76" t="n">
-        <v>13179804.85</v>
+        <v>13411596.02</v>
       </c>
       <c r="G76" t="n">
-        <v>11510927.08</v>
+        <v>11550733.41</v>
       </c>
       <c r="H76" t="n">
-        <v>50585699.32</v>
+        <v>51343341.32</v>
       </c>
       <c r="I76" t="n">
-        <v>47319399.62</v>
+        <v>48295203.35</v>
       </c>
     </row>
     <row r="77">
@@ -2872,19 +2872,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>26607344.26</v>
+        <v>27034536.18</v>
       </c>
       <c r="F77" t="n">
-        <v>22085520.18</v>
+        <v>22593574.63</v>
       </c>
       <c r="G77" t="n">
-        <v>19744337.53</v>
+        <v>19838049.86</v>
       </c>
       <c r="H77" t="n">
-        <v>18154376.27</v>
+        <v>18437538.13</v>
       </c>
       <c r="I77" t="n">
-        <v>29303994.63</v>
+        <v>29560256.11</v>
       </c>
     </row>
     <row r="78">
@@ -2905,19 +2905,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>970087628.3099999</v>
+        <v>1006729227.37</v>
       </c>
       <c r="F78" t="n">
-        <v>739096255.62</v>
+        <v>789724586.1799999</v>
       </c>
       <c r="G78" t="n">
-        <v>713367442.08</v>
+        <v>730432732.89</v>
       </c>
       <c r="H78" t="n">
-        <v>157440192.63</v>
+        <v>159791173.32</v>
       </c>
       <c r="I78" t="n">
-        <v>352178826.45</v>
+        <v>354610776.27</v>
       </c>
     </row>
     <row r="79">
@@ -2938,19 +2938,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>189602554.73</v>
+        <v>196196101.39</v>
       </c>
       <c r="F79" t="n">
-        <v>138321317.18</v>
+        <v>142209823.95</v>
       </c>
       <c r="G79" t="n">
-        <v>107916254.16</v>
+        <v>123085397.37</v>
       </c>
       <c r="H79" t="n">
-        <v>62673101.03</v>
+        <v>62728120.45</v>
       </c>
       <c r="I79" t="n">
-        <v>66788140.89</v>
+        <v>66909624.03</v>
       </c>
     </row>
     <row r="80">
@@ -2971,13 +2971,13 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>30864031.14</v>
+        <v>30966771.6</v>
       </c>
       <c r="F80" t="n">
-        <v>27066019.4</v>
+        <v>28944388.68</v>
       </c>
       <c r="G80" t="n">
-        <v>24770980.49</v>
+        <v>26689466.29</v>
       </c>
       <c r="H80" t="n">
         <v>4983225.57</v>
@@ -3004,19 +3004,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>53720447.55</v>
+        <v>52657678.74</v>
       </c>
       <c r="F81" t="n">
-        <v>30520466.38</v>
+        <v>30766096.28</v>
       </c>
       <c r="G81" t="n">
-        <v>26978325.24</v>
+        <v>28165225.66</v>
       </c>
       <c r="H81" t="n">
-        <v>93035965.29000001</v>
+        <v>94099156.5</v>
       </c>
       <c r="I81" t="n">
-        <v>149841879.2</v>
+        <v>150573760.87</v>
       </c>
     </row>
     <row r="82">
@@ -3037,19 +3037,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>610001632.2</v>
+        <v>612460905.1900001</v>
       </c>
       <c r="F82" t="n">
-        <v>451888200.92</v>
+        <v>465395304.46</v>
       </c>
       <c r="G82" t="n">
-        <v>428692401.42</v>
+        <v>434496763.76</v>
       </c>
       <c r="H82" t="n">
-        <v>145105621.93</v>
+        <v>146730635.18</v>
       </c>
       <c r="I82" t="n">
-        <v>152617812.4</v>
+        <v>153360465.53</v>
       </c>
     </row>
     <row r="83">
@@ -3070,16 +3070,16 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>31743384.51</v>
+        <v>32282647.4</v>
       </c>
       <c r="F83" t="n">
-        <v>27291253.35</v>
+        <v>27549409.09</v>
       </c>
       <c r="G83" t="n">
-        <v>23579319.56</v>
+        <v>24158133.74</v>
       </c>
       <c r="H83" t="n">
-        <v>4788552.39</v>
+        <v>4788551.39</v>
       </c>
       <c r="I83" t="n">
         <v>8287439.25</v>
@@ -3103,19 +3103,19 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>283562979.71</v>
+        <v>285834306.86</v>
       </c>
       <c r="F84" t="n">
-        <v>216285129.65</v>
+        <v>222006344.94</v>
       </c>
       <c r="G84" t="n">
-        <v>188584148.63</v>
+        <v>198608848.47</v>
       </c>
       <c r="H84" t="n">
-        <v>74964907.94</v>
+        <v>75058362.14</v>
       </c>
       <c r="I84" t="n">
-        <v>99677843.55</v>
+        <v>100538632.16</v>
       </c>
     </row>
     <row r="85">
@@ -3136,13 +3136,13 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>95543759.13</v>
+        <v>102617773.9</v>
       </c>
       <c r="F85" t="n">
-        <v>70049664.89</v>
+        <v>77671583.79000001</v>
       </c>
       <c r="G85" t="n">
-        <v>59149824.92</v>
+        <v>59747697.55</v>
       </c>
       <c r="H85" t="n">
         <v>34371578.38</v>
@@ -3169,19 +3169,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>10099744.05</v>
+        <v>10201402.34</v>
       </c>
       <c r="F86" t="n">
-        <v>8427815.470000001</v>
+        <v>8543464.720000001</v>
       </c>
       <c r="G86" t="n">
-        <v>7504646.16</v>
+        <v>7703699.65</v>
       </c>
       <c r="H86" t="n">
-        <v>5342633.4</v>
+        <v>5417295.29</v>
       </c>
       <c r="I86" t="n">
-        <v>4795259.2</v>
+        <v>4857975.21</v>
       </c>
     </row>
     <row r="87">
@@ -3205,10 +3205,10 @@
         <v>5662062.43</v>
       </c>
       <c r="F87" t="n">
-        <v>4760884.23</v>
+        <v>5062438.43</v>
       </c>
       <c r="G87" t="n">
-        <v>3036744.6</v>
+        <v>3325369.25</v>
       </c>
       <c r="H87" t="n">
         <v>624962.6800000001</v>
@@ -3235,19 +3235,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>68528819.48999999</v>
+        <v>68210920.43000001</v>
       </c>
       <c r="F88" t="n">
-        <v>48467299.88</v>
+        <v>50717662.41</v>
       </c>
       <c r="G88" t="n">
-        <v>43141302.15</v>
+        <v>45257398.82</v>
       </c>
       <c r="H88" t="n">
-        <v>20790468.79</v>
+        <v>20790670.7</v>
       </c>
       <c r="I88" t="n">
-        <v>19992125.98</v>
+        <v>20001368.73</v>
       </c>
     </row>
     <row r="89">
@@ -3268,19 +3268,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>57419511.15</v>
+        <v>58497349.88</v>
       </c>
       <c r="F89" t="n">
-        <v>41113437.23</v>
+        <v>42035424.38</v>
       </c>
       <c r="G89" t="n">
-        <v>36756683.13</v>
+        <v>37596257.7</v>
       </c>
       <c r="H89" t="n">
-        <v>25671551.83</v>
+        <v>25767839.5</v>
       </c>
       <c r="I89" t="n">
-        <v>23666371.42</v>
+        <v>23758391.12</v>
       </c>
     </row>
     <row r="90">
@@ -3301,13 +3301,13 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2351482.68</v>
+        <v>2357268.84</v>
       </c>
       <c r="F90" t="n">
-        <v>2086137.58</v>
+        <v>2086149.58</v>
       </c>
       <c r="G90" t="n">
-        <v>1832442.34</v>
+        <v>1832454.34</v>
       </c>
       <c r="H90" t="n">
         <v>294468.9</v>

--- a/upload/orgao2026.xlsx
+++ b/upload/orgao2026.xlsx
@@ -493,19 +493,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>22964754.83</v>
+        <v>22956678.24</v>
       </c>
       <c r="F2" t="n">
-        <v>17796454.15</v>
+        <v>18350271.74</v>
       </c>
       <c r="G2" t="n">
-        <v>15711605.91</v>
+        <v>16255145.41</v>
       </c>
       <c r="H2" t="n">
-        <v>2739450.58</v>
+        <v>2789679.75</v>
       </c>
       <c r="I2" t="n">
-        <v>216945307.51</v>
+        <v>216998772.24</v>
       </c>
     </row>
     <row r="3">
@@ -529,10 +529,10 @@
         <v>1988237.21</v>
       </c>
       <c r="F3" t="n">
-        <v>1823331.67</v>
+        <v>1826653.67</v>
       </c>
       <c r="G3" t="n">
-        <v>1568745.9</v>
+        <v>1572067.9</v>
       </c>
       <c r="H3" t="n">
         <v>60903.67</v>
@@ -559,19 +559,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>181123157.12</v>
+        <v>183603333.2</v>
       </c>
       <c r="F4" t="n">
-        <v>123062207.36</v>
+        <v>124179457.31</v>
       </c>
       <c r="G4" t="n">
-        <v>101966314.82</v>
+        <v>113192013.01</v>
       </c>
       <c r="H4" t="n">
-        <v>35437295.33</v>
+        <v>35551879.99</v>
       </c>
       <c r="I4" t="n">
-        <v>32828534.51</v>
+        <v>32873554.14</v>
       </c>
     </row>
     <row r="5">
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2860947.26</v>
+        <v>3494495.18</v>
       </c>
       <c r="F5" t="n">
-        <v>1782779.57</v>
+        <v>1960637.06</v>
       </c>
       <c r="G5" t="n">
-        <v>1536922.89</v>
+        <v>1549822.58</v>
       </c>
       <c r="H5" t="n">
         <v>706301.5699999999</v>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2534743.44</v>
+        <v>2585551.93</v>
       </c>
       <c r="F6" t="n">
-        <v>1525006.73</v>
+        <v>1684285.71</v>
       </c>
       <c r="G6" t="n">
-        <v>1435208.41</v>
+        <v>1575624</v>
       </c>
       <c r="H6" t="n">
         <v>155417.57</v>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>25002305.35</v>
+        <v>25422305.35</v>
       </c>
       <c r="F7" t="n">
         <v>19790080.52</v>
@@ -691,19 +691,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>80080190.81</v>
+        <v>79762309.5</v>
       </c>
       <c r="F8" t="n">
-        <v>34674047.28</v>
+        <v>37375555.28</v>
       </c>
       <c r="G8" t="n">
-        <v>29956635.23</v>
+        <v>32407791.28</v>
       </c>
       <c r="H8" t="n">
-        <v>51984004.75</v>
+        <v>52321838.63</v>
       </c>
       <c r="I8" t="n">
-        <v>49956435.51</v>
+        <v>50695824.12</v>
       </c>
     </row>
     <row r="9">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3484649.64</v>
+        <v>3583490.7</v>
       </c>
       <c r="F9" t="n">
-        <v>2892131.78</v>
+        <v>2903593.24</v>
       </c>
       <c r="G9" t="n">
-        <v>2607121.32</v>
+        <v>2799336.4</v>
       </c>
       <c r="H9" t="n">
         <v>1345976.77</v>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>84028469.56999999</v>
+        <v>87885328.73</v>
       </c>
       <c r="F10" t="n">
-        <v>79689833.90000001</v>
+        <v>80839190.43000001</v>
       </c>
       <c r="G10" t="n">
-        <v>66929218.67</v>
+        <v>72303299.48999999</v>
       </c>
       <c r="H10" t="n">
         <v>14925708.98</v>
@@ -790,19 +790,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1622787372.01</v>
+        <v>1701399308.48</v>
       </c>
       <c r="F11" t="n">
-        <v>843533995.0700001</v>
+        <v>888314189.0700001</v>
       </c>
       <c r="G11" t="n">
-        <v>819480688.91</v>
+        <v>826232286.08</v>
       </c>
       <c r="H11" t="n">
-        <v>338841681.47</v>
+        <v>346673737.84</v>
       </c>
       <c r="I11" t="n">
-        <v>346228341.19</v>
+        <v>352122145.87</v>
       </c>
     </row>
     <row r="12">
@@ -823,13 +823,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>32788395.03</v>
+        <v>42258002.41</v>
       </c>
       <c r="F12" t="n">
-        <v>16913469.15</v>
+        <v>19567036.53</v>
       </c>
       <c r="G12" t="n">
-        <v>12696575.19</v>
+        <v>18121672.08</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -891,7 +891,7 @@
         <v>789994.92</v>
       </c>
       <c r="G14" t="n">
-        <v>663142.76</v>
+        <v>719150.36</v>
       </c>
       <c r="H14" t="n">
         <v>932410.0600000001</v>
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8686779.15</v>
+        <v>8722111.300000001</v>
       </c>
       <c r="F19" t="n">
-        <v>4437938.21</v>
+        <v>4807403.63</v>
       </c>
       <c r="G19" t="n">
-        <v>4065982.23</v>
+        <v>4283745.57</v>
       </c>
       <c r="H19" t="n">
         <v>1040158.72</v>
@@ -1097,10 +1097,10 @@
         <v>1009317.92</v>
       </c>
       <c r="F21" t="n">
-        <v>850442.89</v>
+        <v>852521.6800000001</v>
       </c>
       <c r="G21" t="n">
-        <v>705315.21</v>
+        <v>707304.6899999999</v>
       </c>
       <c r="H21" t="n">
         <v>97349.38</v>
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>19519429.76</v>
+        <v>20858029.82</v>
       </c>
       <c r="F22" t="n">
-        <v>16588828.63</v>
+        <v>17214281.38</v>
       </c>
       <c r="G22" t="n">
-        <v>14694032.82</v>
+        <v>15260921.03</v>
       </c>
       <c r="H22" t="n">
         <v>4348132.84</v>
@@ -1160,13 +1160,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>9939388.289999999</v>
+        <v>10076113.84</v>
       </c>
       <c r="F23" t="n">
-        <v>8009614.81</v>
+        <v>9059689.4</v>
       </c>
       <c r="G23" t="n">
-        <v>7075379.22</v>
+        <v>7992131.2</v>
       </c>
       <c r="H23" t="n">
         <v>1741057.76</v>
@@ -1202,10 +1202,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2122233.46</v>
+        <v>2323442.46</v>
       </c>
       <c r="I24" t="n">
-        <v>2020366.24</v>
+        <v>2211917.21</v>
       </c>
     </row>
     <row r="25">
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>11752364.48</v>
+        <v>12839677.66</v>
       </c>
       <c r="F26" t="n">
-        <v>4613249.44</v>
+        <v>5051432.5</v>
       </c>
       <c r="G26" t="n">
-        <v>4379359.54</v>
+        <v>4839496.45</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -1284,13 +1284,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>10326294.24</v>
+        <v>10548741.59</v>
       </c>
       <c r="F27" t="n">
-        <v>10005422.98</v>
+        <v>10263168.18</v>
       </c>
       <c r="G27" t="n">
-        <v>7786999.03</v>
+        <v>8428596.25</v>
       </c>
       <c r="H27" t="n">
         <v>1102594.36</v>
@@ -1317,19 +1317,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>9141817.49</v>
+        <v>9298969.779999999</v>
       </c>
       <c r="F28" t="n">
-        <v>7203499.54</v>
+        <v>7739075.36</v>
       </c>
       <c r="G28" t="n">
-        <v>6323518.64</v>
+        <v>6801368.28</v>
       </c>
       <c r="H28" t="n">
         <v>1499694.06</v>
       </c>
       <c r="I28" t="n">
-        <v>2008315.56</v>
+        <v>2013361.26</v>
       </c>
     </row>
     <row r="29">
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3850872.47</v>
+        <v>5852228.28</v>
       </c>
       <c r="F30" t="n">
-        <v>1987053.07</v>
+        <v>2210255.59</v>
       </c>
       <c r="G30" t="n">
-        <v>1894368.53</v>
+        <v>1967366.97</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -1460,19 +1460,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>14205719.8</v>
+        <v>14777982.01</v>
       </c>
       <c r="F33" t="n">
-        <v>10406370.48</v>
+        <v>10446295.65</v>
       </c>
       <c r="G33" t="n">
-        <v>9178462.51</v>
+        <v>9322195.050000001</v>
       </c>
       <c r="H33" t="n">
-        <v>33176516.48</v>
+        <v>33487575.47</v>
       </c>
       <c r="I33" t="n">
-        <v>32348214.72</v>
+        <v>32655541.01</v>
       </c>
     </row>
     <row r="34">
@@ -1493,19 +1493,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1488604375.03</v>
+        <v>1601789114.29</v>
       </c>
       <c r="F34" t="n">
-        <v>1119826614.67</v>
+        <v>1205565161.53</v>
       </c>
       <c r="G34" t="n">
-        <v>966181211.83</v>
+        <v>1020129676.09</v>
       </c>
       <c r="H34" t="n">
-        <v>268651744.87</v>
+        <v>268653701.87</v>
       </c>
       <c r="I34" t="n">
-        <v>249998388.71</v>
+        <v>249999751.53</v>
       </c>
     </row>
     <row r="35">
@@ -1526,19 +1526,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>965772356.1799999</v>
+        <v>1019348675.46</v>
       </c>
       <c r="F35" t="n">
-        <v>592416074.5599999</v>
+        <v>634710240.26</v>
       </c>
       <c r="G35" t="n">
-        <v>526924979.41</v>
+        <v>546956327.53</v>
       </c>
       <c r="H35" t="n">
-        <v>575919628.8200001</v>
+        <v>585262611.38</v>
       </c>
       <c r="I35" t="n">
-        <v>1027604802.87</v>
+        <v>1193709090.58</v>
       </c>
     </row>
     <row r="36">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>45010853.56</v>
+        <v>46962121.84</v>
       </c>
       <c r="F36" t="n">
-        <v>14099885.53</v>
+        <v>14283728.22</v>
       </c>
       <c r="G36" t="n">
-        <v>12641629.3</v>
+        <v>13381796.42</v>
       </c>
       <c r="H36" t="n">
-        <v>44402351.55</v>
+        <v>45931123.98</v>
       </c>
       <c r="I36" t="n">
-        <v>45305846.54</v>
+        <v>46991711.71</v>
       </c>
     </row>
     <row r="37">
@@ -1595,10 +1595,10 @@
         <v>411364.79</v>
       </c>
       <c r="F37" t="n">
-        <v>332205.11</v>
+        <v>365756.59</v>
       </c>
       <c r="G37" t="n">
-        <v>311058.43</v>
+        <v>340662.44</v>
       </c>
       <c r="H37" t="n">
         <v>1251438.8</v>
@@ -1652,19 +1652,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>18768517.53</v>
+        <v>18982797.74</v>
       </c>
       <c r="F39" t="n">
-        <v>11089972.48</v>
+        <v>11212343.02</v>
       </c>
       <c r="G39" t="n">
-        <v>10617739.62</v>
+        <v>10734941.15</v>
       </c>
       <c r="H39" t="n">
-        <v>2161550.53</v>
+        <v>2202227.08</v>
       </c>
       <c r="I39" t="n">
-        <v>2125889.21</v>
+        <v>2163375.46</v>
       </c>
     </row>
     <row r="40">
@@ -1685,19 +1685,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>509125527.9</v>
+        <v>526495589.51</v>
       </c>
       <c r="F40" t="n">
-        <v>416174404.29</v>
+        <v>428616766.95</v>
       </c>
       <c r="G40" t="n">
-        <v>366024577.84</v>
+        <v>390801984.63</v>
       </c>
       <c r="H40" t="n">
-        <v>99813715.72</v>
+        <v>100149338.74</v>
       </c>
       <c r="I40" t="n">
-        <v>100613543.18</v>
+        <v>100820984.47</v>
       </c>
     </row>
     <row r="41">
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>8325868.29</v>
+        <v>8415977.41</v>
       </c>
       <c r="F43" t="n">
-        <v>7157428</v>
+        <v>7208936.31</v>
       </c>
       <c r="G43" t="n">
-        <v>6075686.75</v>
+        <v>6129295.67</v>
       </c>
       <c r="H43" t="n">
         <v>2576363.8</v>
@@ -1847,10 +1847,10 @@
         <v>595515563.95</v>
       </c>
       <c r="F45" t="n">
-        <v>246638164.48</v>
+        <v>262584855.84</v>
       </c>
       <c r="G45" t="n">
-        <v>216615430.98</v>
+        <v>241894432.91</v>
       </c>
       <c r="H45" t="n">
         <v>38776739.66</v>
@@ -1877,19 +1877,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1732263.47</v>
+        <v>1640025.48</v>
       </c>
       <c r="F46" t="n">
-        <v>1052946.96</v>
+        <v>1080915.45</v>
       </c>
       <c r="G46" t="n">
-        <v>954583.67</v>
+        <v>983349.53</v>
       </c>
       <c r="H46" t="n">
-        <v>178281.27</v>
+        <v>179553.95</v>
       </c>
       <c r="I46" t="n">
-        <v>177706.84</v>
+        <v>201015.49</v>
       </c>
     </row>
     <row r="47">
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>216122326.56</v>
+        <v>218803357.34</v>
       </c>
       <c r="F49" t="n">
-        <v>151627268.83</v>
+        <v>153519278.07</v>
       </c>
       <c r="G49" t="n">
-        <v>132375564.95</v>
+        <v>142579207.61</v>
       </c>
       <c r="H49" t="n">
         <v>136515156.77</v>
       </c>
       <c r="I49" t="n">
-        <v>141000459.38</v>
+        <v>141000881.74</v>
       </c>
     </row>
     <row r="50">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>15780207.31</v>
+        <v>16560503.14</v>
       </c>
       <c r="F50" t="n">
         <v>15045689.09</v>
@@ -2006,10 +2006,10 @@
         <v>14437836.75</v>
       </c>
       <c r="H50" t="n">
-        <v>19814010.18</v>
+        <v>19826917.03</v>
       </c>
       <c r="I50" t="n">
-        <v>21160337.38</v>
+        <v>21171782.63</v>
       </c>
     </row>
     <row r="51">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>105171538.95</v>
+        <v>119141744.95</v>
       </c>
       <c r="F51" t="n">
-        <v>61200749.74</v>
+        <v>64456443.08</v>
       </c>
       <c r="G51" t="n">
-        <v>56948967.43</v>
+        <v>59911920.71</v>
       </c>
       <c r="H51" t="n">
         <v>18617499.53</v>
@@ -2063,13 +2063,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>49837193.49</v>
+        <v>50800857.99</v>
       </c>
       <c r="F52" t="n">
-        <v>22255848.04</v>
+        <v>22560566.7</v>
       </c>
       <c r="G52" t="n">
-        <v>19172013</v>
+        <v>20018021.3</v>
       </c>
       <c r="H52" t="n">
         <v>12470050.72</v>
@@ -2123,19 +2123,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>145271780.36</v>
+        <v>149558602.23</v>
       </c>
       <c r="F54" t="n">
-        <v>114467766.22</v>
+        <v>118298994.54</v>
       </c>
       <c r="G54" t="n">
-        <v>102278124.83</v>
+        <v>106215005.07</v>
       </c>
       <c r="H54" t="n">
-        <v>24493382.91</v>
+        <v>24523761.26</v>
       </c>
       <c r="I54" t="n">
-        <v>27303259.79</v>
+        <v>27318113.28</v>
       </c>
     </row>
     <row r="55">
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>29810353.41</v>
+        <v>30717670.21</v>
       </c>
       <c r="F55" t="n">
-        <v>24100045.8</v>
+        <v>24176954.15</v>
       </c>
       <c r="G55" t="n">
-        <v>23417539.66</v>
+        <v>23544441.83</v>
       </c>
       <c r="H55" t="n">
-        <v>22140382.18</v>
+        <v>22207352.89</v>
       </c>
       <c r="I55" t="n">
-        <v>22890160.12</v>
+        <v>22956327.18</v>
       </c>
     </row>
     <row r="56">
@@ -2189,19 +2189,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>46455276.75</v>
+        <v>47017227.03</v>
       </c>
       <c r="F56" t="n">
-        <v>41014666.72</v>
+        <v>41513702.27</v>
       </c>
       <c r="G56" t="n">
-        <v>32796558.59</v>
+        <v>34915188.96</v>
       </c>
       <c r="H56" t="n">
-        <v>8629501.859999999</v>
+        <v>8695024.720000001</v>
       </c>
       <c r="I56" t="n">
-        <v>8371087.11</v>
+        <v>8433246.51</v>
       </c>
     </row>
     <row r="57">
@@ -2222,13 +2222,13 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4717218.3</v>
+        <v>6317926.74</v>
       </c>
       <c r="F57" t="n">
-        <v>4003129.8</v>
+        <v>4006710.02</v>
       </c>
       <c r="G57" t="n">
-        <v>3569130.7</v>
+        <v>3571701.79</v>
       </c>
       <c r="H57" t="n">
         <v>532120.09</v>
@@ -2255,13 +2255,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>7022646.38</v>
+        <v>7080593.53</v>
       </c>
       <c r="F58" t="n">
-        <v>4922637.29</v>
+        <v>4982534.6</v>
       </c>
       <c r="G58" t="n">
-        <v>4601239.52</v>
+        <v>4660885.55</v>
       </c>
       <c r="H58" t="n">
         <v>11029049.85</v>
@@ -2288,19 +2288,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>14202817.76</v>
+        <v>14627112.87</v>
       </c>
       <c r="F59" t="n">
-        <v>9076000.09</v>
+        <v>9740605.51</v>
       </c>
       <c r="G59" t="n">
-        <v>8399636.689999999</v>
+        <v>8906213.869999999</v>
       </c>
       <c r="H59" t="n">
-        <v>5237570.34</v>
+        <v>5238435.34</v>
       </c>
       <c r="I59" t="n">
-        <v>5538957.19</v>
+        <v>5539822.19</v>
       </c>
     </row>
     <row r="60">
@@ -2321,13 +2321,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>10895862.68</v>
+        <v>10906159.48</v>
       </c>
       <c r="F60" t="n">
-        <v>10149198.57</v>
+        <v>10504520.18</v>
       </c>
       <c r="G60" t="n">
-        <v>8999066.859999999</v>
+        <v>9335184.5</v>
       </c>
       <c r="H60" t="n">
         <v>1332496.42</v>
@@ -2383,19 +2383,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>241270000.98</v>
+        <v>248359309.73</v>
       </c>
       <c r="F62" t="n">
-        <v>199826895.97</v>
+        <v>204893558.93</v>
       </c>
       <c r="G62" t="n">
-        <v>184757680.36</v>
+        <v>189695132.88</v>
       </c>
       <c r="H62" t="n">
-        <v>199082035.29</v>
+        <v>199147526.86</v>
       </c>
       <c r="I62" t="n">
-        <v>194368466.05</v>
+        <v>194467740.51</v>
       </c>
     </row>
     <row r="63">
@@ -2416,19 +2416,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>67980365.77</v>
+        <v>69891435.05</v>
       </c>
       <c r="F63" t="n">
-        <v>53728205.92</v>
+        <v>54745972.98</v>
       </c>
       <c r="G63" t="n">
-        <v>48626257.12</v>
+        <v>49162011.5</v>
       </c>
       <c r="H63" t="n">
-        <v>35392441.77</v>
+        <v>35399302.22</v>
       </c>
       <c r="I63" t="n">
-        <v>53948333.28</v>
+        <v>53976596.69</v>
       </c>
     </row>
     <row r="64">
@@ -2449,13 +2449,13 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>11619061.16</v>
+        <v>11632286.88</v>
       </c>
       <c r="F64" t="n">
-        <v>8338706.58</v>
+        <v>9151184.35</v>
       </c>
       <c r="G64" t="n">
-        <v>7809048.74</v>
+        <v>7956756.45</v>
       </c>
       <c r="H64" t="n">
         <v>1960878.57</v>
@@ -2482,13 +2482,13 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>626618.0699999999</v>
+        <v>631415.9300000001</v>
       </c>
       <c r="F65" t="n">
-        <v>571577.77</v>
+        <v>575472.14</v>
       </c>
       <c r="G65" t="n">
-        <v>494572.91</v>
+        <v>498467.28</v>
       </c>
       <c r="H65" t="n">
         <v>34744.58</v>
@@ -2545,10 +2545,10 @@
         <v>1467968.73</v>
       </c>
       <c r="F67" t="n">
-        <v>1228701.65</v>
+        <v>1350347.99</v>
       </c>
       <c r="G67" t="n">
-        <v>1139013.87</v>
+        <v>1248614.17</v>
       </c>
       <c r="H67" t="n">
         <v>94595.71000000001</v>
@@ -2575,19 +2575,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>248019910.24</v>
+        <v>260499656.6</v>
       </c>
       <c r="F68" t="n">
-        <v>191229727.31</v>
+        <v>194074161.17</v>
       </c>
       <c r="G68" t="n">
-        <v>174521870.25</v>
+        <v>180176226.6</v>
       </c>
       <c r="H68" t="n">
-        <v>53256400.68</v>
+        <v>54952605</v>
       </c>
       <c r="I68" t="n">
-        <v>60344287.52</v>
+        <v>60455000.88</v>
       </c>
     </row>
     <row r="69">
@@ -2608,19 +2608,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>274678795.42</v>
+        <v>296143456.05</v>
       </c>
       <c r="F69" t="n">
-        <v>199868797.86</v>
+        <v>205661334.62</v>
       </c>
       <c r="G69" t="n">
-        <v>172892523.36</v>
+        <v>178686826.67</v>
       </c>
       <c r="H69" t="n">
-        <v>89356852.52</v>
+        <v>89803011.59999999</v>
       </c>
       <c r="I69" t="n">
-        <v>85236865.42</v>
+        <v>86653163.95</v>
       </c>
     </row>
     <row r="70">
@@ -2641,19 +2641,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>506420728.52</v>
+        <v>533876189.91</v>
       </c>
       <c r="F70" t="n">
-        <v>347095331.01</v>
+        <v>373730732.06</v>
       </c>
       <c r="G70" t="n">
-        <v>292653309.75</v>
+        <v>325064615.43</v>
       </c>
       <c r="H70" t="n">
-        <v>244247142.58</v>
+        <v>260222996.61</v>
       </c>
       <c r="I70" t="n">
-        <v>206328788.11</v>
+        <v>267157232.9</v>
       </c>
     </row>
     <row r="71">
@@ -2677,10 +2677,10 @@
         <v>1091554.25</v>
       </c>
       <c r="F71" t="n">
-        <v>1063776.19</v>
+        <v>1065221.29</v>
       </c>
       <c r="G71" t="n">
-        <v>952134.78</v>
+        <v>953545.2</v>
       </c>
       <c r="H71" t="n">
         <v>225243.01</v>
@@ -2707,13 +2707,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>58821482.15</v>
+        <v>60679875.33</v>
       </c>
       <c r="F72" t="n">
-        <v>38851490.85</v>
+        <v>39297531.31</v>
       </c>
       <c r="G72" t="n">
-        <v>37375031.76</v>
+        <v>37792622.98</v>
       </c>
       <c r="H72" t="n">
         <v>19576645.24</v>
@@ -2743,10 +2743,10 @@
         <v>1785466.95</v>
       </c>
       <c r="F73" t="n">
-        <v>1575389.44</v>
+        <v>1639587.31</v>
       </c>
       <c r="G73" t="n">
-        <v>1366656.76</v>
+        <v>1448600.41</v>
       </c>
       <c r="H73" t="n">
         <v>34378.25</v>
@@ -2773,19 +2773,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>108711330.48</v>
+        <v>125298330.48</v>
       </c>
       <c r="F74" t="n">
-        <v>66326632.83</v>
+        <v>67909805</v>
       </c>
       <c r="G74" t="n">
-        <v>62062183.61</v>
+        <v>63972378.05</v>
       </c>
       <c r="H74" t="n">
-        <v>66894090.28</v>
+        <v>67991185.53</v>
       </c>
       <c r="I74" t="n">
-        <v>63485193.53</v>
+        <v>64552244.64</v>
       </c>
     </row>
     <row r="75">
@@ -2806,13 +2806,13 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>19297933.07</v>
+        <v>20112244.59</v>
       </c>
       <c r="F75" t="n">
-        <v>16337873.19</v>
+        <v>16353533.04</v>
       </c>
       <c r="G75" t="n">
-        <v>13912090.11</v>
+        <v>13926968.06</v>
       </c>
       <c r="H75" t="n">
         <v>674995.91</v>
@@ -2839,19 +2839,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>243275271.49</v>
+        <v>243280003.49</v>
       </c>
       <c r="F76" t="n">
-        <v>13411596.02</v>
+        <v>13921497.85</v>
       </c>
       <c r="G76" t="n">
-        <v>11550733.41</v>
+        <v>12109029.32</v>
       </c>
       <c r="H76" t="n">
-        <v>51343341.32</v>
+        <v>57479423.59</v>
       </c>
       <c r="I76" t="n">
-        <v>48295203.35</v>
+        <v>49013872.43</v>
       </c>
     </row>
     <row r="77">
@@ -2872,19 +2872,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>27034536.18</v>
+        <v>28120618.19</v>
       </c>
       <c r="F77" t="n">
-        <v>22593574.63</v>
+        <v>23706632.26</v>
       </c>
       <c r="G77" t="n">
-        <v>19838049.86</v>
+        <v>21683890.87</v>
       </c>
       <c r="H77" t="n">
-        <v>18437538.13</v>
+        <v>19120037.92</v>
       </c>
       <c r="I77" t="n">
-        <v>29560256.11</v>
+        <v>29992876.71</v>
       </c>
     </row>
     <row r="78">
@@ -2905,19 +2905,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1006729227.37</v>
+        <v>1081952053.55</v>
       </c>
       <c r="F78" t="n">
-        <v>789724586.1799999</v>
+        <v>820366890.92</v>
       </c>
       <c r="G78" t="n">
-        <v>730432732.89</v>
+        <v>791498482.6799999</v>
       </c>
       <c r="H78" t="n">
-        <v>159791173.32</v>
+        <v>161065340.54</v>
       </c>
       <c r="I78" t="n">
-        <v>354610776.27</v>
+        <v>358000507.11</v>
       </c>
     </row>
     <row r="79">
@@ -2938,19 +2938,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>196196101.39</v>
+        <v>197785774.2</v>
       </c>
       <c r="F79" t="n">
-        <v>142209823.95</v>
+        <v>145070067.67</v>
       </c>
       <c r="G79" t="n">
-        <v>123085397.37</v>
+        <v>126241653.09</v>
       </c>
       <c r="H79" t="n">
-        <v>62728120.45</v>
+        <v>63251609.55</v>
       </c>
       <c r="I79" t="n">
-        <v>66909624.03</v>
+        <v>67402184.83</v>
       </c>
     </row>
     <row r="80">
@@ -2971,13 +2971,13 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>30966771.6</v>
+        <v>32309252.4</v>
       </c>
       <c r="F80" t="n">
-        <v>28944388.68</v>
+        <v>29255642.12</v>
       </c>
       <c r="G80" t="n">
-        <v>26689466.29</v>
+        <v>26802072.1</v>
       </c>
       <c r="H80" t="n">
         <v>4983225.57</v>
@@ -3004,19 +3004,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>52657678.74</v>
+        <v>54671839.17</v>
       </c>
       <c r="F81" t="n">
-        <v>30766096.28</v>
+        <v>32431200.53</v>
       </c>
       <c r="G81" t="n">
-        <v>28165225.66</v>
+        <v>30137390.04</v>
       </c>
       <c r="H81" t="n">
-        <v>94099156.5</v>
+        <v>95236830.48</v>
       </c>
       <c r="I81" t="n">
-        <v>150573760.87</v>
+        <v>150834041.74</v>
       </c>
     </row>
     <row r="82">
@@ -3037,19 +3037,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>612460905.1900001</v>
+        <v>622768242.65</v>
       </c>
       <c r="F82" t="n">
-        <v>465395304.46</v>
+        <v>484242340.15</v>
       </c>
       <c r="G82" t="n">
-        <v>434496763.76</v>
+        <v>456741255.72</v>
       </c>
       <c r="H82" t="n">
-        <v>146730635.18</v>
+        <v>149649355.04</v>
       </c>
       <c r="I82" t="n">
-        <v>153360465.53</v>
+        <v>155588916.99</v>
       </c>
     </row>
     <row r="83">
@@ -3070,19 +3070,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>32282647.4</v>
+        <v>34016469.06</v>
       </c>
       <c r="F83" t="n">
-        <v>27549409.09</v>
+        <v>29821574.69</v>
       </c>
       <c r="G83" t="n">
-        <v>24158133.74</v>
+        <v>25392998.24</v>
       </c>
       <c r="H83" t="n">
-        <v>4788551.39</v>
+        <v>4788587.37</v>
       </c>
       <c r="I83" t="n">
-        <v>8287439.25</v>
+        <v>8287475.23</v>
       </c>
     </row>
     <row r="84">
@@ -3103,19 +3103,19 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>285834306.86</v>
+        <v>280480162.99</v>
       </c>
       <c r="F84" t="n">
-        <v>222006344.94</v>
+        <v>230946318.46</v>
       </c>
       <c r="G84" t="n">
-        <v>198608848.47</v>
+        <v>206684563.77</v>
       </c>
       <c r="H84" t="n">
-        <v>75058362.14</v>
+        <v>75060983.79000001</v>
       </c>
       <c r="I84" t="n">
-        <v>100538632.16</v>
+        <v>100540986.26</v>
       </c>
     </row>
     <row r="85">
@@ -3136,13 +3136,13 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>102617773.9</v>
+        <v>103697441.64</v>
       </c>
       <c r="F85" t="n">
-        <v>77671583.79000001</v>
+        <v>80585179.92</v>
       </c>
       <c r="G85" t="n">
-        <v>59747697.55</v>
+        <v>66854227.46</v>
       </c>
       <c r="H85" t="n">
         <v>34371578.38</v>
@@ -3169,13 +3169,13 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>10201402.34</v>
+        <v>10846954.23</v>
       </c>
       <c r="F86" t="n">
-        <v>8543464.720000001</v>
+        <v>8682537.08</v>
       </c>
       <c r="G86" t="n">
-        <v>7703699.65</v>
+        <v>7819956.46</v>
       </c>
       <c r="H86" t="n">
         <v>5417295.29</v>
@@ -3205,10 +3205,10 @@
         <v>5662062.43</v>
       </c>
       <c r="F87" t="n">
-        <v>5062438.43</v>
+        <v>5077205.53</v>
       </c>
       <c r="G87" t="n">
-        <v>3325369.25</v>
+        <v>3937838.27</v>
       </c>
       <c r="H87" t="n">
         <v>624962.6800000001</v>
@@ -3235,19 +3235,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>68210920.43000001</v>
+        <v>68563725.09999999</v>
       </c>
       <c r="F88" t="n">
-        <v>50717662.41</v>
+        <v>52040070.13</v>
       </c>
       <c r="G88" t="n">
-        <v>45257398.82</v>
+        <v>46518622.77</v>
       </c>
       <c r="H88" t="n">
-        <v>20790670.7</v>
+        <v>20927257.25</v>
       </c>
       <c r="I88" t="n">
-        <v>20001368.73</v>
+        <v>20118616.38</v>
       </c>
     </row>
     <row r="89">
@@ -3268,19 +3268,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>58497349.88</v>
+        <v>60189105.19</v>
       </c>
       <c r="F89" t="n">
-        <v>42035424.38</v>
+        <v>43727902.52</v>
       </c>
       <c r="G89" t="n">
-        <v>37596257.7</v>
+        <v>39218854.52</v>
       </c>
       <c r="H89" t="n">
-        <v>25767839.5</v>
+        <v>25987757.85</v>
       </c>
       <c r="I89" t="n">
-        <v>23758391.12</v>
+        <v>23968091.22</v>
       </c>
     </row>
     <row r="90">
@@ -3304,10 +3304,10 @@
         <v>2357268.84</v>
       </c>
       <c r="F90" t="n">
-        <v>2086149.58</v>
+        <v>2088302.75</v>
       </c>
       <c r="G90" t="n">
-        <v>1832454.34</v>
+        <v>1834504.16</v>
       </c>
       <c r="H90" t="n">
         <v>294468.9</v>

--- a/upload/orgao2026.xlsx
+++ b/upload/orgao2026.xlsx
@@ -952,19 +952,19 @@
         <v>98</v>
       </c>
       <c r="E2">
-        <v>22853325.29</v>
+        <v>23612427.57</v>
       </c>
       <c r="F2">
-        <v>18437580.59</v>
+        <v>18640214.34</v>
       </c>
       <c r="G2">
-        <v>16913165.14</v>
+        <v>16999299.57</v>
       </c>
       <c r="H2">
-        <v>2813790.06</v>
+        <v>2847052.9</v>
       </c>
       <c r="I2">
-        <v>216995992.02</v>
+        <v>216994912.01</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -984,10 +984,10 @@
         <v>1988342.21</v>
       </c>
       <c r="F3">
-        <v>1827542.67</v>
+        <v>1847373.44</v>
       </c>
       <c r="G3">
-        <v>1572956.9</v>
+        <v>1592641.68</v>
       </c>
       <c r="H3">
         <v>60903.67</v>
@@ -1010,19 +1010,19 @@
         <v>100</v>
       </c>
       <c r="E4">
-        <v>183914743.99</v>
+        <v>214742000.38</v>
       </c>
       <c r="F4">
-        <v>126574024.29</v>
+        <v>128527275.49</v>
       </c>
       <c r="G4">
-        <v>114279069.77</v>
+        <v>115055401.06</v>
       </c>
       <c r="H4">
         <v>35939229.14</v>
       </c>
       <c r="I4">
-        <v>32982832.11</v>
+        <v>33370181.26</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1039,13 +1039,13 @@
         <v>101</v>
       </c>
       <c r="E5">
-        <v>3501892.18</v>
+        <v>3486020.39</v>
       </c>
       <c r="F5">
-        <v>2058212.39</v>
+        <v>2085734.22</v>
       </c>
       <c r="G5">
-        <v>1689594.07</v>
+        <v>1716523.49</v>
       </c>
       <c r="H5">
         <v>706301.5699999999</v>
@@ -1068,19 +1068,19 @@
         <v>102</v>
       </c>
       <c r="E6">
-        <v>2570397.67</v>
+        <v>2665277.33</v>
       </c>
       <c r="F6">
-        <v>1684285.71</v>
+        <v>1698521.62</v>
       </c>
       <c r="G6">
-        <v>1581443.94</v>
+        <v>1595212.96</v>
       </c>
       <c r="H6">
-        <v>155417.57</v>
+        <v>163691.57</v>
       </c>
       <c r="I6">
-        <v>150004.18</v>
+        <v>158278.18</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1097,13 +1097,13 @@
         <v>103</v>
       </c>
       <c r="E7">
-        <v>22689317.76</v>
+        <v>26384999.26</v>
       </c>
       <c r="F7">
-        <v>20928980.21</v>
+        <v>22183311.49</v>
       </c>
       <c r="G7">
-        <v>18713176.74</v>
+        <v>19677769.55</v>
       </c>
       <c r="H7">
         <v>2353030.07</v>
@@ -1126,19 +1126,19 @@
         <v>104</v>
       </c>
       <c r="E8">
-        <v>81080538.69</v>
+        <v>83957578.34999999</v>
       </c>
       <c r="F8">
-        <v>38332326.9</v>
+        <v>39947646.21</v>
       </c>
       <c r="G8">
-        <v>33867141.52</v>
+        <v>35421664.09</v>
       </c>
       <c r="H8">
-        <v>52525654.42</v>
+        <v>54238467.1</v>
       </c>
       <c r="I8">
-        <v>51846660.91</v>
+        <v>52134974.69</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1155,13 +1155,13 @@
         <v>105</v>
       </c>
       <c r="E9">
-        <v>3583554.71</v>
+        <v>3592507.18</v>
       </c>
       <c r="F9">
-        <v>2996502.36</v>
+        <v>3007163.23</v>
       </c>
       <c r="G9">
-        <v>2815722.4</v>
+        <v>2896191.28</v>
       </c>
       <c r="H9">
         <v>1345976.77</v>
@@ -1184,13 +1184,13 @@
         <v>106</v>
       </c>
       <c r="E10">
-        <v>88276867.44</v>
+        <v>98017049.44</v>
       </c>
       <c r="F10">
-        <v>81006576.68000001</v>
+        <v>82211933.06</v>
       </c>
       <c r="G10">
-        <v>72548926.81999999</v>
+        <v>73109084.78</v>
       </c>
       <c r="H10">
         <v>14925708.98</v>
@@ -1213,19 +1213,19 @@
         <v>107</v>
       </c>
       <c r="E11">
-        <v>1758136907.5</v>
+        <v>1839424121.76</v>
       </c>
       <c r="F11">
-        <v>958284767.1900001</v>
+        <v>1006243706.16</v>
       </c>
       <c r="G11">
-        <v>925045475.15</v>
+        <v>978873972.86</v>
       </c>
       <c r="H11">
-        <v>350566812.91</v>
+        <v>355321725.1</v>
       </c>
       <c r="I11">
-        <v>355506404.61</v>
+        <v>361404266.6</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1242,13 +1242,13 @@
         <v>108</v>
       </c>
       <c r="E12">
-        <v>44736648.85</v>
+        <v>52331272.27</v>
       </c>
       <c r="F12">
-        <v>24459888.2</v>
+        <v>37779474.48</v>
       </c>
       <c r="G12">
-        <v>23012941.27</v>
+        <v>36321231.1</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1297,7 +1297,7 @@
         <v>2193789.5</v>
       </c>
       <c r="F14">
-        <v>789994.92</v>
+        <v>953326.64</v>
       </c>
       <c r="G14">
         <v>719150.36</v>
@@ -1406,19 +1406,19 @@
         <v>115</v>
       </c>
       <c r="E19">
-        <v>8777833.27</v>
+        <v>8790091.289999999</v>
       </c>
       <c r="F19">
-        <v>4843220.43</v>
+        <v>5020968.74</v>
       </c>
       <c r="G19">
-        <v>4427715.3</v>
+        <v>4591674.92</v>
       </c>
       <c r="H19">
-        <v>1040174.78</v>
+        <v>1045788.75</v>
       </c>
       <c r="I19">
-        <v>1179226.69</v>
+        <v>1183994</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1438,10 +1438,10 @@
         <v>358206</v>
       </c>
       <c r="F20">
-        <v>243531.59</v>
+        <v>254375.91</v>
       </c>
       <c r="G20">
-        <v>230061.11</v>
+        <v>240905.43</v>
       </c>
       <c r="H20">
         <v>30324.78</v>
@@ -1464,13 +1464,13 @@
         <v>117</v>
       </c>
       <c r="E21">
-        <v>1017356.81</v>
+        <v>1019739.15</v>
       </c>
       <c r="F21">
-        <v>951400.13</v>
+        <v>959254.26</v>
       </c>
       <c r="G21">
-        <v>708719.1800000001</v>
+        <v>812140.13</v>
       </c>
       <c r="H21">
         <v>97349.38</v>
@@ -1493,19 +1493,19 @@
         <v>118</v>
       </c>
       <c r="E22">
-        <v>20920813.91</v>
+        <v>21625914.36</v>
       </c>
       <c r="F22">
-        <v>18604943.23</v>
+        <v>18706697.11</v>
       </c>
       <c r="G22">
-        <v>16557848.69</v>
+        <v>16596942.81</v>
       </c>
       <c r="H22">
-        <v>4348132.84</v>
+        <v>4350382.84</v>
       </c>
       <c r="I22">
-        <v>7649550.61</v>
+        <v>7652352.61</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1522,19 +1522,19 @@
         <v>119</v>
       </c>
       <c r="E23">
-        <v>10093673.84</v>
+        <v>10232292.48</v>
       </c>
       <c r="F23">
-        <v>9452593.369999999</v>
+        <v>9545322.859999999</v>
       </c>
       <c r="G23">
-        <v>8381580.37</v>
+        <v>8447201.92</v>
       </c>
       <c r="H23">
-        <v>1773350.18</v>
+        <v>1776239.78</v>
       </c>
       <c r="I23">
-        <v>2481676.97</v>
+        <v>2516592.76</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1626,13 +1626,13 @@
         <v>123</v>
       </c>
       <c r="E27">
-        <v>10564374.4</v>
+        <v>10898932.59</v>
       </c>
       <c r="F27">
-        <v>10275198.52</v>
+        <v>10538095.18</v>
       </c>
       <c r="G27">
-        <v>8734809.439999999</v>
+        <v>8773120.369999999</v>
       </c>
       <c r="H27">
         <v>1102594.36</v>
@@ -1655,13 +1655,13 @@
         <v>124</v>
       </c>
       <c r="E28">
-        <v>9318686.34</v>
+        <v>9497576.789999999</v>
       </c>
       <c r="F28">
-        <v>7782026.2</v>
+        <v>7964542.12</v>
       </c>
       <c r="G28">
-        <v>6842505.37</v>
+        <v>7022592.03</v>
       </c>
       <c r="H28">
         <v>1499694.06</v>
@@ -1704,13 +1704,13 @@
         <v>126</v>
       </c>
       <c r="E30">
-        <v>6082268.28</v>
+        <v>6239262.24</v>
       </c>
       <c r="F30">
-        <v>2210255.59</v>
+        <v>2213338.23</v>
       </c>
       <c r="G30">
-        <v>2180887.46</v>
+        <v>2181572.24</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1767,13 +1767,13 @@
         <v>129</v>
       </c>
       <c r="E33">
-        <v>14859767.01</v>
+        <v>16151401.61</v>
       </c>
       <c r="F33">
-        <v>10451360.61</v>
+        <v>10905353.79</v>
       </c>
       <c r="G33">
-        <v>9353923.140000001</v>
+        <v>9710366.529999999</v>
       </c>
       <c r="H33">
         <v>33487575.47</v>
@@ -1796,13 +1796,13 @@
         <v>130</v>
       </c>
       <c r="E34">
-        <v>1633475502.27</v>
+        <v>1677546712.95</v>
       </c>
       <c r="F34">
-        <v>1247085569.86</v>
+        <v>1311861169.5</v>
       </c>
       <c r="G34">
-        <v>1060590172.42</v>
+        <v>1132143716.34</v>
       </c>
       <c r="H34">
         <v>268654858.87</v>
@@ -1825,19 +1825,19 @@
         <v>131</v>
       </c>
       <c r="E35">
-        <v>1049586261.13</v>
+        <v>1080046616.55</v>
       </c>
       <c r="F35">
-        <v>664672635.73</v>
+        <v>691490916.36</v>
       </c>
       <c r="G35">
-        <v>586066678.64</v>
+        <v>623253049.73</v>
       </c>
       <c r="H35">
-        <v>596232679.51</v>
+        <v>597041663.9299999</v>
       </c>
       <c r="I35">
-        <v>1229096996.24</v>
+        <v>1239893929.2</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1854,19 +1854,19 @@
         <v>132</v>
       </c>
       <c r="E36">
-        <v>47588310.96</v>
+        <v>51709729.92</v>
       </c>
       <c r="F36">
-        <v>15160307.45</v>
+        <v>15867029.77</v>
       </c>
       <c r="G36">
-        <v>13777086.68</v>
+        <v>14224438.89</v>
       </c>
       <c r="H36">
         <v>46057549.98</v>
       </c>
       <c r="I36">
-        <v>47611727.75</v>
+        <v>52179185.66</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -1883,7 +1883,7 @@
         <v>133</v>
       </c>
       <c r="E37">
-        <v>411364.79</v>
+        <v>413829.9</v>
       </c>
       <c r="F37">
         <v>365756.59</v>
@@ -1932,19 +1932,19 @@
         <v>135</v>
       </c>
       <c r="E39">
-        <v>19842229.66</v>
+        <v>19899813.26</v>
       </c>
       <c r="F39">
-        <v>12166385.89</v>
+        <v>12426212.47</v>
       </c>
       <c r="G39">
-        <v>11538528.44</v>
+        <v>11813737.72</v>
       </c>
       <c r="H39">
-        <v>2213034.08</v>
+        <v>2222214.48</v>
       </c>
       <c r="I39">
-        <v>2176754.96</v>
+        <v>2185825.2</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -1961,19 +1961,19 @@
         <v>136</v>
       </c>
       <c r="E40">
-        <v>533980073.33</v>
+        <v>540658324.85</v>
       </c>
       <c r="F40">
-        <v>443846643.78</v>
+        <v>459822068.77</v>
       </c>
       <c r="G40">
-        <v>396485326.27</v>
+        <v>398769379.71</v>
       </c>
       <c r="H40">
-        <v>100335395.6</v>
+        <v>100533880.65</v>
       </c>
       <c r="I40">
-        <v>100842427.13</v>
+        <v>101192747.95</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -2019,7 +2019,7 @@
         <v>138</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>86400</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2039,13 +2039,13 @@
         <v>139</v>
       </c>
       <c r="E43">
-        <v>9031559.039999999</v>
+        <v>9120631.24</v>
       </c>
       <c r="F43">
-        <v>7217098.82</v>
+        <v>7234653.51</v>
       </c>
       <c r="G43">
-        <v>6324360.74</v>
+        <v>6340908.59</v>
       </c>
       <c r="H43">
         <v>2576363.8</v>
@@ -2068,10 +2068,10 @@
         <v>140</v>
       </c>
       <c r="E44">
-        <v>6123226.75</v>
+        <v>8538886.66</v>
       </c>
       <c r="F44">
-        <v>23226.75</v>
+        <v>24558.97</v>
       </c>
       <c r="G44">
         <v>22948.03</v>
@@ -2100,10 +2100,10 @@
         <v>595515563.95</v>
       </c>
       <c r="F45">
-        <v>262584855.84</v>
+        <v>265784585.78</v>
       </c>
       <c r="G45">
-        <v>241894432.91</v>
+        <v>244780589.31</v>
       </c>
       <c r="H45">
         <v>38776739.66</v>
@@ -2126,13 +2126,13 @@
         <v>142</v>
       </c>
       <c r="E46">
-        <v>1645146.87</v>
+        <v>1944330.21</v>
       </c>
       <c r="F46">
-        <v>1095402.06</v>
+        <v>1122712.31</v>
       </c>
       <c r="G46">
-        <v>990449.17</v>
+        <v>1017643.09</v>
       </c>
       <c r="H46">
         <v>179553.95</v>
@@ -2195,19 +2195,19 @@
         <v>145</v>
       </c>
       <c r="E49">
-        <v>278203874.28</v>
+        <v>281489596.25</v>
       </c>
       <c r="F49">
-        <v>156149668.07</v>
+        <v>157313385.78</v>
       </c>
       <c r="G49">
-        <v>146369452.43</v>
+        <v>150760738.78</v>
       </c>
       <c r="H49">
-        <v>136515156.76</v>
+        <v>136601196.75</v>
       </c>
       <c r="I49">
-        <v>141000881.74</v>
+        <v>142170179.74</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -2227,10 +2227,10 @@
         <v>16579515.63</v>
       </c>
       <c r="F50">
-        <v>15525089.09</v>
+        <v>15763101.58</v>
       </c>
       <c r="G50">
-        <v>14870580.75</v>
+        <v>15362327.84</v>
       </c>
       <c r="H50">
         <v>19826917.03</v>
@@ -2253,13 +2253,13 @@
         <v>147</v>
       </c>
       <c r="E51">
-        <v>119002701.32</v>
+        <v>119647706.97</v>
       </c>
       <c r="F51">
-        <v>67745657.45999999</v>
+        <v>70635381.39</v>
       </c>
       <c r="G51">
-        <v>63059438.14</v>
+        <v>64314580.49</v>
       </c>
       <c r="H51">
         <v>18617499.53</v>
@@ -2282,13 +2282,13 @@
         <v>148</v>
       </c>
       <c r="E52">
-        <v>49632030.16</v>
+        <v>50135892.42</v>
       </c>
       <c r="F52">
-        <v>23362376.95</v>
+        <v>23514946.97</v>
       </c>
       <c r="G52">
-        <v>20227807.97</v>
+        <v>21023787.88</v>
       </c>
       <c r="H52">
         <v>12470050.72</v>
@@ -2331,19 +2331,19 @@
         <v>150</v>
       </c>
       <c r="E54">
-        <v>149920606.24</v>
+        <v>158346285.65</v>
       </c>
       <c r="F54">
-        <v>122580095.61</v>
+        <v>128772380.44</v>
       </c>
       <c r="G54">
-        <v>109732413.73</v>
+        <v>115248890.76</v>
       </c>
       <c r="H54">
-        <v>24537392.35</v>
+        <v>24667775.39</v>
       </c>
       <c r="I54">
-        <v>27318113.28</v>
+        <v>27387945.61</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -2360,19 +2360,19 @@
         <v>151</v>
       </c>
       <c r="E55">
-        <v>31653032.32</v>
+        <v>33668830.62</v>
       </c>
       <c r="F55">
-        <v>25195829.05</v>
+        <v>26884531.65</v>
       </c>
       <c r="G55">
-        <v>23964892.18</v>
+        <v>25513340.53</v>
       </c>
       <c r="H55">
-        <v>22250403.13</v>
+        <v>22624961.53</v>
       </c>
       <c r="I55">
-        <v>22999377.42</v>
+        <v>23373935.82</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -2389,13 +2389,13 @@
         <v>152</v>
       </c>
       <c r="E56">
-        <v>47290432.59</v>
+        <v>53249320.3</v>
       </c>
       <c r="F56">
-        <v>42077358.15</v>
+        <v>44149560.74</v>
       </c>
       <c r="G56">
-        <v>35746226.02</v>
+        <v>37173394.77</v>
       </c>
       <c r="H56">
         <v>8695024.720000001</v>
@@ -2418,13 +2418,13 @@
         <v>153</v>
       </c>
       <c r="E57">
-        <v>6300076.74</v>
+        <v>6351925.43</v>
       </c>
       <c r="F57">
-        <v>4009110.02</v>
+        <v>4438349.62</v>
       </c>
       <c r="G57">
-        <v>3573866.59</v>
+        <v>3661611.07</v>
       </c>
       <c r="H57">
         <v>585363.28</v>
@@ -2447,13 +2447,13 @@
         <v>154</v>
       </c>
       <c r="E58">
-        <v>7122065.58</v>
+        <v>7367863.27</v>
       </c>
       <c r="F58">
-        <v>4989268.03</v>
+        <v>6278064.57</v>
       </c>
       <c r="G58">
-        <v>4667541.79</v>
+        <v>5956049.77</v>
       </c>
       <c r="H58">
         <v>11029049.85</v>
@@ -2476,13 +2476,13 @@
         <v>155</v>
       </c>
       <c r="E59">
-        <v>14993895.58</v>
+        <v>15190245.09</v>
       </c>
       <c r="F59">
-        <v>9875588.24</v>
+        <v>10003642.01</v>
       </c>
       <c r="G59">
-        <v>9190488.310000001</v>
+        <v>9299047.890000001</v>
       </c>
       <c r="H59">
         <v>5238435.34</v>
@@ -2505,13 +2505,13 @@
         <v>156</v>
       </c>
       <c r="E60">
-        <v>10937876.6</v>
+        <v>11427155.81</v>
       </c>
       <c r="F60">
-        <v>10526285.4</v>
+        <v>10678763.36</v>
       </c>
       <c r="G60">
-        <v>9356515.15</v>
+        <v>9384241.800000001</v>
       </c>
       <c r="H60">
         <v>1332496.42</v>
@@ -2557,19 +2557,19 @@
         <v>158</v>
       </c>
       <c r="E62">
-        <v>260191109.04</v>
+        <v>264309178.14</v>
       </c>
       <c r="F62">
-        <v>209952061.67</v>
+        <v>214905790.39</v>
       </c>
       <c r="G62">
-        <v>194410184.7</v>
+        <v>198070418.99</v>
       </c>
       <c r="H62">
-        <v>199214974.5</v>
+        <v>199241931.12</v>
       </c>
       <c r="I62">
-        <v>194534961.92</v>
+        <v>194560643.74</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -2586,19 +2586,19 @@
         <v>159</v>
       </c>
       <c r="E63">
-        <v>70266030.17</v>
+        <v>74330418.38</v>
       </c>
       <c r="F63">
-        <v>55391189.2</v>
+        <v>56439020.41</v>
       </c>
       <c r="G63">
-        <v>49941525.82</v>
+        <v>51058502.79</v>
       </c>
       <c r="H63">
-        <v>35498418.32</v>
+        <v>35587470.8</v>
       </c>
       <c r="I63">
-        <v>54018413.74</v>
+        <v>54117902.32</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -2618,10 +2618,10 @@
         <v>11632286.88</v>
       </c>
       <c r="F64">
-        <v>9268299.25</v>
+        <v>9287887.23</v>
       </c>
       <c r="G64">
-        <v>8064218.75</v>
+        <v>8743906.619999999</v>
       </c>
       <c r="H64">
         <v>1960878.57</v>
@@ -2644,13 +2644,13 @@
         <v>161</v>
       </c>
       <c r="E65">
-        <v>631415.9300000001</v>
+        <v>731805.9300000001</v>
       </c>
       <c r="F65">
-        <v>577601.73</v>
+        <v>587546.46</v>
       </c>
       <c r="G65">
-        <v>500596.87</v>
+        <v>510301.8</v>
       </c>
       <c r="H65">
         <v>34744.58</v>
@@ -2693,13 +2693,13 @@
         <v>163</v>
       </c>
       <c r="E67">
-        <v>1474748.43</v>
+        <v>1475088.13</v>
       </c>
       <c r="F67">
-        <v>1350347.99</v>
+        <v>1354242.36</v>
       </c>
       <c r="G67">
-        <v>1248614.17</v>
+        <v>1252508.54</v>
       </c>
       <c r="H67">
         <v>94595.71000000001</v>
@@ -2722,19 +2722,19 @@
         <v>164</v>
       </c>
       <c r="E68">
-        <v>259360242.28</v>
+        <v>266762466.33</v>
       </c>
       <c r="F68">
-        <v>195988099.2</v>
+        <v>203836961.33</v>
       </c>
       <c r="G68">
-        <v>184860222.73</v>
+        <v>186569321.48</v>
       </c>
       <c r="H68">
-        <v>55006594.97</v>
+        <v>55051157.61</v>
       </c>
       <c r="I68">
-        <v>60550509.6</v>
+        <v>60641733.47</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -2751,19 +2751,19 @@
         <v>165</v>
       </c>
       <c r="E69">
-        <v>300894088.62</v>
+        <v>310728351.95</v>
       </c>
       <c r="F69">
-        <v>228450572.45</v>
+        <v>233246913.17</v>
       </c>
       <c r="G69">
-        <v>199145490.82</v>
+        <v>202940330.5</v>
       </c>
       <c r="H69">
-        <v>91872946.45999999</v>
+        <v>91876339.38</v>
       </c>
       <c r="I69">
-        <v>88830264.33</v>
+        <v>88839854.8</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -2780,19 +2780,19 @@
         <v>166</v>
       </c>
       <c r="E70">
-        <v>546339886.4299999</v>
+        <v>559532373.97</v>
       </c>
       <c r="F70">
-        <v>383321267.56</v>
+        <v>396071508.92</v>
       </c>
       <c r="G70">
-        <v>333158320.6</v>
+        <v>275084313.9</v>
       </c>
       <c r="H70">
-        <v>260789413.28</v>
+        <v>260924471.54</v>
       </c>
       <c r="I70">
-        <v>267379884.39</v>
+        <v>267428072.35</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -2809,13 +2809,13 @@
         <v>167</v>
       </c>
       <c r="E71">
-        <v>1123663.41</v>
+        <v>1129934.24</v>
       </c>
       <c r="F71">
-        <v>1065221.29</v>
+        <v>1102441.65</v>
       </c>
       <c r="G71">
-        <v>953545.2</v>
+        <v>984963.39</v>
       </c>
       <c r="H71">
         <v>225243.01</v>
@@ -2841,10 +2841,10 @@
         <v>62658228.81</v>
       </c>
       <c r="F72">
-        <v>40702391.86</v>
+        <v>40917682.44</v>
       </c>
       <c r="G72">
-        <v>39049631.55</v>
+        <v>39248919.45</v>
       </c>
       <c r="H72">
         <v>19576645.24</v>
@@ -2867,13 +2867,13 @@
         <v>169</v>
       </c>
       <c r="E73">
-        <v>1949827.57</v>
+        <v>1951588.53</v>
       </c>
       <c r="F73">
-        <v>1645634.25</v>
+        <v>1854616.61</v>
       </c>
       <c r="G73">
-        <v>1454358.74</v>
+        <v>1478589.79</v>
       </c>
       <c r="H73">
         <v>34378.25</v>
@@ -2896,19 +2896,19 @@
         <v>170</v>
       </c>
       <c r="E74">
-        <v>124633564.77</v>
+        <v>124760964.67</v>
       </c>
       <c r="F74">
-        <v>69218409.11</v>
+        <v>70394879.22</v>
       </c>
       <c r="G74">
-        <v>65617066.9</v>
+        <v>66048632.08</v>
       </c>
       <c r="H74">
-        <v>68053748.56999999</v>
+        <v>68490777.18000001</v>
       </c>
       <c r="I74">
-        <v>64671094.54</v>
+        <v>64895141.78</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -2925,13 +2925,13 @@
         <v>171</v>
       </c>
       <c r="E75">
-        <v>22847921.73</v>
+        <v>23091951.84</v>
       </c>
       <c r="F75">
-        <v>16756771.5</v>
+        <v>17873715.48</v>
       </c>
       <c r="G75">
-        <v>14294410.5</v>
+        <v>14545966.69</v>
       </c>
       <c r="H75">
         <v>674995.91</v>
@@ -2954,19 +2954,19 @@
         <v>172</v>
       </c>
       <c r="E76">
-        <v>243335282.11</v>
+        <v>244424975.99</v>
       </c>
       <c r="F76">
-        <v>13961759.73</v>
+        <v>13994305.33</v>
       </c>
       <c r="G76">
-        <v>12453611.88</v>
+        <v>12478206.3</v>
       </c>
       <c r="H76">
-        <v>58024715.19</v>
+        <v>58510718.79</v>
       </c>
       <c r="I76">
-        <v>54767606.11</v>
+        <v>55214148.64</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -2983,19 +2983,19 @@
         <v>173</v>
       </c>
       <c r="E77">
-        <v>28797756.1</v>
+        <v>29191047.41</v>
       </c>
       <c r="F77">
-        <v>24721038.16</v>
+        <v>24903655.77</v>
       </c>
       <c r="G77">
-        <v>22656413.7</v>
+        <v>22839531.14</v>
       </c>
       <c r="H77">
-        <v>19305726.79</v>
+        <v>19722571.84</v>
       </c>
       <c r="I77">
-        <v>30163440.95</v>
+        <v>30501377.48</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -3012,19 +3012,19 @@
         <v>174</v>
       </c>
       <c r="E78">
-        <v>1099377501.85</v>
+        <v>1123312635.13</v>
       </c>
       <c r="F78">
-        <v>840558139.37</v>
+        <v>854784510.9</v>
       </c>
       <c r="G78">
-        <v>810648927.25</v>
+        <v>826336317.21</v>
       </c>
       <c r="H78">
-        <v>161675963.5</v>
+        <v>161989712.75</v>
       </c>
       <c r="I78">
-        <v>358409835.78</v>
+        <v>358867940.53</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -3041,16 +3041,16 @@
         <v>175</v>
       </c>
       <c r="E79">
-        <v>198346147.39</v>
+        <v>202041161.36</v>
       </c>
       <c r="F79">
-        <v>147029630.78</v>
+        <v>160334112.92</v>
       </c>
       <c r="G79">
-        <v>131844130.17</v>
+        <v>134266309.14</v>
       </c>
       <c r="H79">
-        <v>63251609.55</v>
+        <v>63256021.9</v>
       </c>
       <c r="I79">
         <v>67834742.25</v>
@@ -3070,13 +3070,13 @@
         <v>176</v>
       </c>
       <c r="E80">
-        <v>35376453.93</v>
+        <v>36883900.73</v>
       </c>
       <c r="F80">
-        <v>29513675.28</v>
+        <v>33272577.59</v>
       </c>
       <c r="G80">
-        <v>26824704.92</v>
+        <v>28967333.12</v>
       </c>
       <c r="H80">
         <v>4983225.57</v>
@@ -3099,19 +3099,19 @@
         <v>177</v>
       </c>
       <c r="E81">
-        <v>58273169.37</v>
+        <v>58640469.78</v>
       </c>
       <c r="F81">
-        <v>34455319.12</v>
+        <v>36565561.71</v>
       </c>
       <c r="G81">
-        <v>30769517.79</v>
+        <v>33821449.89</v>
       </c>
       <c r="H81">
-        <v>95447724.87</v>
+        <v>96263747.28</v>
       </c>
       <c r="I81">
-        <v>152381873.54</v>
+        <v>152910770.7</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -3128,19 +3128,19 @@
         <v>178</v>
       </c>
       <c r="E82">
-        <v>662024777.3</v>
+        <v>699542763.37</v>
       </c>
       <c r="F82">
-        <v>504078590.33</v>
+        <v>513029492.18</v>
       </c>
       <c r="G82">
-        <v>474551322.5</v>
+        <v>483109992.42</v>
       </c>
       <c r="H82">
-        <v>156942356.02</v>
+        <v>157600145.61</v>
       </c>
       <c r="I82">
-        <v>155874741.18</v>
+        <v>158556440.29</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -3157,13 +3157,13 @@
         <v>179</v>
       </c>
       <c r="E83">
-        <v>36596912.32</v>
+        <v>36832065.82</v>
       </c>
       <c r="F83">
-        <v>30344199.46</v>
+        <v>35429728.06</v>
       </c>
       <c r="G83">
-        <v>26477779.46</v>
+        <v>27121135.84</v>
       </c>
       <c r="H83">
         <v>4788587.37</v>
@@ -3186,19 +3186,19 @@
         <v>180</v>
       </c>
       <c r="E84">
-        <v>286930392.8</v>
+        <v>286387941.34</v>
       </c>
       <c r="F84">
-        <v>235775341.25</v>
+        <v>240724500.19</v>
       </c>
       <c r="G84">
-        <v>214623166.43</v>
+        <v>217780517.05</v>
       </c>
       <c r="H84">
         <v>75127332</v>
       </c>
       <c r="I84">
-        <v>100615001.99</v>
+        <v>100674914.42</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -3215,13 +3215,13 @@
         <v>181</v>
       </c>
       <c r="E85">
-        <v>103977798.08</v>
+        <v>109983811.04</v>
       </c>
       <c r="F85">
-        <v>81630780.03</v>
+        <v>81954107.45999999</v>
       </c>
       <c r="G85">
-        <v>68541416.40000001</v>
+        <v>69479979.03</v>
       </c>
       <c r="H85">
         <v>34371578.38</v>
@@ -3244,19 +3244,19 @@
         <v>182</v>
       </c>
       <c r="E86">
-        <v>11672594.34</v>
+        <v>11697041.21</v>
       </c>
       <c r="F86">
-        <v>9329569.060000001</v>
+        <v>10030599.88</v>
       </c>
       <c r="G86">
-        <v>8382450.28</v>
+        <v>8928663.029999999</v>
       </c>
       <c r="H86">
-        <v>5462913.94</v>
+        <v>5521109.94</v>
       </c>
       <c r="I86">
-        <v>5272922.03</v>
+        <v>5326919.47</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -3273,10 +3273,10 @@
         <v>183</v>
       </c>
       <c r="E87">
-        <v>5712648.54</v>
+        <v>6040468.66</v>
       </c>
       <c r="F87">
-        <v>5085890.53</v>
+        <v>5569365.56</v>
       </c>
       <c r="G87">
         <v>4030449.14</v>
@@ -3302,13 +3302,13 @@
         <v>184</v>
       </c>
       <c r="E88">
-        <v>69079262.90000001</v>
+        <v>75679642.8</v>
       </c>
       <c r="F88">
-        <v>52807307.44</v>
+        <v>53289940.68</v>
       </c>
       <c r="G88">
-        <v>47291660.52</v>
+        <v>47724632.71</v>
       </c>
       <c r="H88">
         <v>20927257.25</v>
@@ -3331,13 +3331,13 @@
         <v>185</v>
       </c>
       <c r="E89">
-        <v>63859702.48</v>
+        <v>66179318.45</v>
       </c>
       <c r="F89">
-        <v>44609912.73</v>
+        <v>45405682.15</v>
       </c>
       <c r="G89">
-        <v>39970828.41</v>
+        <v>40729380.6</v>
       </c>
       <c r="H89">
         <v>26399033.76</v>
@@ -3360,13 +3360,13 @@
         <v>186</v>
       </c>
       <c r="E90">
-        <v>2598646.97</v>
+        <v>2621464.07</v>
       </c>
       <c r="F90">
-        <v>2104389.43</v>
+        <v>2358341.87</v>
       </c>
       <c r="G90">
-        <v>1850590.84</v>
+        <v>2068656.31</v>
       </c>
       <c r="H90">
         <v>294468.9</v>

--- a/upload/orgao2026.xlsx
+++ b/upload/orgao2026.xlsx
@@ -952,16 +952,16 @@
         <v>98</v>
       </c>
       <c r="E2">
-        <v>23612427.57</v>
+        <v>25539123.85</v>
       </c>
       <c r="F2">
-        <v>18640214.34</v>
+        <v>19816084.07</v>
       </c>
       <c r="G2">
-        <v>16999299.57</v>
+        <v>17089684.83</v>
       </c>
       <c r="H2">
-        <v>2847052.9</v>
+        <v>2899426.92</v>
       </c>
       <c r="I2">
         <v>216994912.01</v>
@@ -981,13 +981,13 @@
         <v>99</v>
       </c>
       <c r="E3">
-        <v>1988342.21</v>
+        <v>2192603.56</v>
       </c>
       <c r="F3">
-        <v>1847373.44</v>
+        <v>1853367.53</v>
       </c>
       <c r="G3">
-        <v>1592641.68</v>
+        <v>1598631.95</v>
       </c>
       <c r="H3">
         <v>60903.67</v>
@@ -1010,16 +1010,16 @@
         <v>100</v>
       </c>
       <c r="E4">
-        <v>214742000.38</v>
+        <v>225929540.73</v>
       </c>
       <c r="F4">
-        <v>128527275.49</v>
+        <v>141568041.78</v>
       </c>
       <c r="G4">
-        <v>115055401.06</v>
+        <v>117171311.06</v>
       </c>
       <c r="H4">
-        <v>35939229.14</v>
+        <v>35939894.14</v>
       </c>
       <c r="I4">
         <v>33370181.26</v>
@@ -1039,13 +1039,13 @@
         <v>101</v>
       </c>
       <c r="E5">
-        <v>3486020.39</v>
+        <v>3536195.3</v>
       </c>
       <c r="F5">
-        <v>2085734.22</v>
+        <v>2087709.56</v>
       </c>
       <c r="G5">
-        <v>1716523.49</v>
+        <v>1718430.16</v>
       </c>
       <c r="H5">
         <v>706301.5699999999</v>
@@ -1068,13 +1068,13 @@
         <v>102</v>
       </c>
       <c r="E6">
-        <v>2665277.33</v>
+        <v>2665524.88</v>
       </c>
       <c r="F6">
-        <v>1698521.62</v>
+        <v>1802619.9</v>
       </c>
       <c r="G6">
-        <v>1595212.96</v>
+        <v>1684118.07</v>
       </c>
       <c r="H6">
         <v>163691.57</v>
@@ -1100,10 +1100,10 @@
         <v>26384999.26</v>
       </c>
       <c r="F7">
-        <v>22183311.49</v>
+        <v>22186764.99</v>
       </c>
       <c r="G7">
-        <v>19677769.55</v>
+        <v>19967540.03</v>
       </c>
       <c r="H7">
         <v>2353030.07</v>
@@ -1126,19 +1126,19 @@
         <v>104</v>
       </c>
       <c r="E8">
-        <v>83957578.34999999</v>
+        <v>89285825.87</v>
       </c>
       <c r="F8">
-        <v>39947646.21</v>
+        <v>41148205.53</v>
       </c>
       <c r="G8">
-        <v>35421664.09</v>
+        <v>36827245.63</v>
       </c>
       <c r="H8">
-        <v>54238467.1</v>
+        <v>54259206.32</v>
       </c>
       <c r="I8">
-        <v>52134974.69</v>
+        <v>53853835.43</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1155,13 +1155,13 @@
         <v>105</v>
       </c>
       <c r="E9">
-        <v>3592507.18</v>
+        <v>3640619.84</v>
       </c>
       <c r="F9">
-        <v>3007163.23</v>
+        <v>3014149.24</v>
       </c>
       <c r="G9">
-        <v>2896191.28</v>
+        <v>2900803.32</v>
       </c>
       <c r="H9">
         <v>1345976.77</v>
@@ -1184,13 +1184,13 @@
         <v>106</v>
       </c>
       <c r="E10">
-        <v>98017049.44</v>
+        <v>101459923.69</v>
       </c>
       <c r="F10">
-        <v>82211933.06</v>
+        <v>88115664.25</v>
       </c>
       <c r="G10">
-        <v>73109084.78</v>
+        <v>75876686.84999999</v>
       </c>
       <c r="H10">
         <v>14925708.98</v>
@@ -1213,19 +1213,19 @@
         <v>107</v>
       </c>
       <c r="E11">
-        <v>1839424121.76</v>
+        <v>2017318864.71</v>
       </c>
       <c r="F11">
-        <v>1006243706.16</v>
+        <v>1024112523.6</v>
       </c>
       <c r="G11">
-        <v>978873972.86</v>
+        <v>990860575.7</v>
       </c>
       <c r="H11">
-        <v>355321725.1</v>
+        <v>358448315.62</v>
       </c>
       <c r="I11">
-        <v>361404266.6</v>
+        <v>363105265.39</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1242,13 +1242,13 @@
         <v>108</v>
       </c>
       <c r="E12">
-        <v>52331272.27</v>
+        <v>52386272.27</v>
       </c>
       <c r="F12">
-        <v>37779474.48</v>
+        <v>37801082.38</v>
       </c>
       <c r="G12">
-        <v>36321231.1</v>
+        <v>36412213.71</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1323,13 +1323,13 @@
         <v>111</v>
       </c>
       <c r="E15">
-        <v>243357094.6</v>
+        <v>277564547.5</v>
       </c>
       <c r="F15">
-        <v>243357094.6</v>
+        <v>277564547.5</v>
       </c>
       <c r="G15">
-        <v>243357094.6</v>
+        <v>277564547.5</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1346,13 +1346,13 @@
         <v>112</v>
       </c>
       <c r="E16">
-        <v>19634354.31</v>
+        <v>21518069.79</v>
       </c>
       <c r="F16">
-        <v>19634354.31</v>
+        <v>21518069.79</v>
       </c>
       <c r="G16">
-        <v>19634354.31</v>
+        <v>21518069.79</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1383,13 +1383,13 @@
         <v>114</v>
       </c>
       <c r="E18">
-        <v>98640447.63</v>
+        <v>112599904.26</v>
       </c>
       <c r="F18">
-        <v>98640447.63</v>
+        <v>112599904.26</v>
       </c>
       <c r="G18">
-        <v>98640447.63</v>
+        <v>112599904.26</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1406,13 +1406,13 @@
         <v>115</v>
       </c>
       <c r="E19">
-        <v>8790091.289999999</v>
+        <v>8816546.73</v>
       </c>
       <c r="F19">
         <v>5020968.74</v>
       </c>
       <c r="G19">
-        <v>4591674.92</v>
+        <v>4599541.1</v>
       </c>
       <c r="H19">
         <v>1045788.75</v>
@@ -1438,10 +1438,10 @@
         <v>358206</v>
       </c>
       <c r="F20">
-        <v>254375.91</v>
+        <v>274479.92</v>
       </c>
       <c r="G20">
-        <v>240905.43</v>
+        <v>259270.43</v>
       </c>
       <c r="H20">
         <v>30324.78</v>
@@ -1464,13 +1464,13 @@
         <v>117</v>
       </c>
       <c r="E21">
-        <v>1019739.15</v>
+        <v>1103756.08</v>
       </c>
       <c r="F21">
-        <v>959254.26</v>
+        <v>1046078.56</v>
       </c>
       <c r="G21">
-        <v>812140.13</v>
+        <v>879403.47</v>
       </c>
       <c r="H21">
         <v>97349.38</v>
@@ -1493,19 +1493,19 @@
         <v>118</v>
       </c>
       <c r="E22">
-        <v>21625914.36</v>
+        <v>22157585.69</v>
       </c>
       <c r="F22">
-        <v>18706697.11</v>
+        <v>19260314.25</v>
       </c>
       <c r="G22">
-        <v>16596942.81</v>
+        <v>17178211.52</v>
       </c>
       <c r="H22">
-        <v>4350382.84</v>
+        <v>4351124.84</v>
       </c>
       <c r="I22">
-        <v>7652352.61</v>
+        <v>7653094.61</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1522,13 +1522,13 @@
         <v>119</v>
       </c>
       <c r="E23">
-        <v>10232292.48</v>
+        <v>11247199.77</v>
       </c>
       <c r="F23">
-        <v>9545322.859999999</v>
+        <v>9574776.85</v>
       </c>
       <c r="G23">
-        <v>8447201.92</v>
+        <v>8476127.57</v>
       </c>
       <c r="H23">
         <v>1776239.78</v>
@@ -1580,7 +1580,7 @@
         <v>121</v>
       </c>
       <c r="E25">
-        <v>35450000</v>
+        <v>12877268.68</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>122</v>
       </c>
       <c r="E26">
-        <v>12852375.66</v>
+        <v>13095226.66</v>
       </c>
       <c r="F26">
         <v>5150669.09</v>
@@ -1626,13 +1626,13 @@
         <v>123</v>
       </c>
       <c r="E27">
-        <v>10898932.59</v>
+        <v>11391214.88</v>
       </c>
       <c r="F27">
-        <v>10538095.18</v>
+        <v>10970840</v>
       </c>
       <c r="G27">
-        <v>8773120.369999999</v>
+        <v>8825559.34</v>
       </c>
       <c r="H27">
         <v>1102594.36</v>
@@ -1655,13 +1655,13 @@
         <v>124</v>
       </c>
       <c r="E28">
-        <v>9497576.789999999</v>
+        <v>10089160.52</v>
       </c>
       <c r="F28">
-        <v>7964542.12</v>
+        <v>8046124.62</v>
       </c>
       <c r="G28">
-        <v>7022592.03</v>
+        <v>6986188.47</v>
       </c>
       <c r="H28">
         <v>1499694.06</v>
@@ -1704,13 +1704,13 @@
         <v>126</v>
       </c>
       <c r="E30">
-        <v>6239262.24</v>
+        <v>18965012.24</v>
       </c>
       <c r="F30">
         <v>2213338.23</v>
       </c>
       <c r="G30">
-        <v>2181572.24</v>
+        <v>2183755.8</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1767,19 +1767,19 @@
         <v>129</v>
       </c>
       <c r="E33">
-        <v>16151401.61</v>
+        <v>16152446.21</v>
       </c>
       <c r="F33">
-        <v>10905353.79</v>
+        <v>10970774.55</v>
       </c>
       <c r="G33">
-        <v>9710366.529999999</v>
+        <v>9827601.710000001</v>
       </c>
       <c r="H33">
-        <v>33487575.47</v>
+        <v>33790513.37</v>
       </c>
       <c r="I33">
-        <v>32655541.01</v>
+        <v>32952437.85</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1796,19 +1796,19 @@
         <v>130</v>
       </c>
       <c r="E34">
-        <v>1677546712.95</v>
+        <v>1709058292.09</v>
       </c>
       <c r="F34">
-        <v>1311861169.5</v>
+        <v>1363462892.17</v>
       </c>
       <c r="G34">
-        <v>1132143716.34</v>
+        <v>1177899393.71</v>
       </c>
       <c r="H34">
-        <v>268654858.87</v>
+        <v>268677608.87</v>
       </c>
       <c r="I34">
-        <v>250003449.06</v>
+        <v>250021582.88</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1825,19 +1825,19 @@
         <v>131</v>
       </c>
       <c r="E35">
-        <v>1080046616.55</v>
+        <v>1099710205.66</v>
       </c>
       <c r="F35">
-        <v>691490916.36</v>
+        <v>710885819.66</v>
       </c>
       <c r="G35">
-        <v>623253049.73</v>
+        <v>631108490.99</v>
       </c>
       <c r="H35">
-        <v>597041663.9299999</v>
+        <v>597159284.46</v>
       </c>
       <c r="I35">
-        <v>1239893929.2</v>
+        <v>1243817987.19</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1854,13 +1854,13 @@
         <v>132</v>
       </c>
       <c r="E36">
-        <v>51709729.92</v>
+        <v>52526713.42</v>
       </c>
       <c r="F36">
-        <v>15867029.77</v>
+        <v>18711649</v>
       </c>
       <c r="G36">
-        <v>14224438.89</v>
+        <v>14543230.08</v>
       </c>
       <c r="H36">
         <v>46057549.98</v>
@@ -1886,10 +1886,10 @@
         <v>413829.9</v>
       </c>
       <c r="F37">
-        <v>365756.59</v>
+        <v>365931.72</v>
       </c>
       <c r="G37">
-        <v>340662.44</v>
+        <v>340829.16</v>
       </c>
       <c r="H37">
         <v>1251438.8</v>
@@ -1932,19 +1932,19 @@
         <v>135</v>
       </c>
       <c r="E39">
-        <v>19899813.26</v>
+        <v>22960966.23</v>
       </c>
       <c r="F39">
-        <v>12426212.47</v>
+        <v>12581820.42</v>
       </c>
       <c r="G39">
-        <v>11813737.72</v>
+        <v>11979758.75</v>
       </c>
       <c r="H39">
-        <v>2222214.48</v>
+        <v>2243300.48</v>
       </c>
       <c r="I39">
-        <v>2185825.2</v>
+        <v>2188196.4</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -1961,16 +1961,16 @@
         <v>136</v>
       </c>
       <c r="E40">
-        <v>540658324.85</v>
+        <v>565708837.63</v>
       </c>
       <c r="F40">
-        <v>459822068.77</v>
+        <v>473304260.51</v>
       </c>
       <c r="G40">
-        <v>398769379.71</v>
+        <v>403593795.5</v>
       </c>
       <c r="H40">
-        <v>100533880.65</v>
+        <v>100875435.59</v>
       </c>
       <c r="I40">
         <v>101192747.95</v>
@@ -1990,10 +1990,10 @@
         <v>137</v>
       </c>
       <c r="E41">
-        <v>222775.76</v>
+        <v>251340.45</v>
       </c>
       <c r="F41">
-        <v>222775.76</v>
+        <v>251340.45</v>
       </c>
       <c r="G41">
         <v>186763.97</v>
@@ -2039,19 +2039,19 @@
         <v>139</v>
       </c>
       <c r="E43">
-        <v>9120631.24</v>
+        <v>11373344.9</v>
       </c>
       <c r="F43">
-        <v>7234653.51</v>
+        <v>7251420.97</v>
       </c>
       <c r="G43">
-        <v>6340908.59</v>
+        <v>6357003.38</v>
       </c>
       <c r="H43">
-        <v>2576363.8</v>
+        <v>2580254.92</v>
       </c>
       <c r="I43">
-        <v>2406586.33</v>
+        <v>2409881.06</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -2074,7 +2074,7 @@
         <v>24558.97</v>
       </c>
       <c r="G44">
-        <v>22948.03</v>
+        <v>24197.65</v>
       </c>
       <c r="H44">
         <v>2205946.03</v>
@@ -2097,13 +2097,13 @@
         <v>141</v>
       </c>
       <c r="E45">
-        <v>595515563.95</v>
+        <v>613399284.2</v>
       </c>
       <c r="F45">
         <v>265784585.78</v>
       </c>
       <c r="G45">
-        <v>244780589.31</v>
+        <v>245003040.75</v>
       </c>
       <c r="H45">
         <v>38776739.66</v>
@@ -2126,13 +2126,13 @@
         <v>142</v>
       </c>
       <c r="E46">
-        <v>1944330.21</v>
+        <v>2094036.11</v>
       </c>
       <c r="F46">
-        <v>1122712.31</v>
+        <v>1244142.89</v>
       </c>
       <c r="G46">
-        <v>1017643.09</v>
+        <v>1117614.55</v>
       </c>
       <c r="H46">
         <v>179553.95</v>
@@ -2195,13 +2195,13 @@
         <v>145</v>
       </c>
       <c r="E49">
-        <v>281489596.25</v>
+        <v>287669662.68</v>
       </c>
       <c r="F49">
-        <v>157313385.78</v>
+        <v>205149384.66</v>
       </c>
       <c r="G49">
-        <v>150760738.78</v>
+        <v>151165469.49</v>
       </c>
       <c r="H49">
         <v>136601196.75</v>
@@ -2233,10 +2233,10 @@
         <v>15362327.84</v>
       </c>
       <c r="H50">
-        <v>19826917.03</v>
+        <v>20051763.81</v>
       </c>
       <c r="I50">
-        <v>21174482.98</v>
+        <v>21396376.22</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -2253,13 +2253,13 @@
         <v>147</v>
       </c>
       <c r="E51">
-        <v>119647706.97</v>
+        <v>120467525.9</v>
       </c>
       <c r="F51">
-        <v>70635381.39</v>
+        <v>72108741.69</v>
       </c>
       <c r="G51">
-        <v>64314580.49</v>
+        <v>67423871.38</v>
       </c>
       <c r="H51">
         <v>18617499.53</v>
@@ -2282,13 +2282,13 @@
         <v>148</v>
       </c>
       <c r="E52">
-        <v>50135892.42</v>
+        <v>48816651.38</v>
       </c>
       <c r="F52">
-        <v>23514946.97</v>
+        <v>23833454.22</v>
       </c>
       <c r="G52">
-        <v>21023787.88</v>
+        <v>21126489.97</v>
       </c>
       <c r="H52">
         <v>12470050.72</v>
@@ -2331,13 +2331,13 @@
         <v>150</v>
       </c>
       <c r="E54">
-        <v>158346285.65</v>
+        <v>160039276.75</v>
       </c>
       <c r="F54">
-        <v>128772380.44</v>
+        <v>133566985.16</v>
       </c>
       <c r="G54">
-        <v>115248890.76</v>
+        <v>117110455.98</v>
       </c>
       <c r="H54">
         <v>24667775.39</v>
@@ -2360,13 +2360,13 @@
         <v>151</v>
       </c>
       <c r="E55">
-        <v>33668830.62</v>
+        <v>34105430.6</v>
       </c>
       <c r="F55">
-        <v>26884531.65</v>
+        <v>26899214.4</v>
       </c>
       <c r="G55">
-        <v>25513340.53</v>
+        <v>26184099.21</v>
       </c>
       <c r="H55">
         <v>22624961.53</v>
@@ -2389,16 +2389,16 @@
         <v>152</v>
       </c>
       <c r="E56">
-        <v>53249320.3</v>
+        <v>54249255.45</v>
       </c>
       <c r="F56">
-        <v>44149560.74</v>
+        <v>47207489.75</v>
       </c>
       <c r="G56">
-        <v>37173394.77</v>
+        <v>37918475.23</v>
       </c>
       <c r="H56">
-        <v>8695024.720000001</v>
+        <v>8896224.32</v>
       </c>
       <c r="I56">
         <v>8434068.029999999</v>
@@ -2418,13 +2418,13 @@
         <v>153</v>
       </c>
       <c r="E57">
-        <v>6351925.43</v>
+        <v>6555670.4</v>
       </c>
       <c r="F57">
-        <v>4438349.62</v>
+        <v>4453405.17</v>
       </c>
       <c r="G57">
-        <v>3661611.07</v>
+        <v>3677336.24</v>
       </c>
       <c r="H57">
         <v>585363.28</v>
@@ -2450,10 +2450,10 @@
         <v>7367863.27</v>
       </c>
       <c r="F58">
-        <v>6278064.57</v>
+        <v>6473497.2</v>
       </c>
       <c r="G58">
-        <v>5956049.77</v>
+        <v>5998624.21</v>
       </c>
       <c r="H58">
         <v>11029049.85</v>
@@ -2476,13 +2476,13 @@
         <v>155</v>
       </c>
       <c r="E59">
-        <v>15190245.09</v>
+        <v>15592653.53</v>
       </c>
       <c r="F59">
-        <v>10003642.01</v>
+        <v>10432018.21</v>
       </c>
       <c r="G59">
-        <v>9299047.890000001</v>
+        <v>9707150.470000001</v>
       </c>
       <c r="H59">
         <v>5238435.34</v>
@@ -2505,13 +2505,13 @@
         <v>156</v>
       </c>
       <c r="E60">
-        <v>11427155.81</v>
+        <v>12363172.47</v>
       </c>
       <c r="F60">
-        <v>10678763.36</v>
+        <v>11931860.24</v>
       </c>
       <c r="G60">
-        <v>9384241.800000001</v>
+        <v>10545805.59</v>
       </c>
       <c r="H60">
         <v>1332496.42</v>
@@ -2534,13 +2534,13 @@
         <v>157</v>
       </c>
       <c r="E61">
-        <v>47222671.95</v>
+        <v>52804838.5</v>
       </c>
       <c r="F61">
-        <v>47222671.95</v>
+        <v>52804838.5</v>
       </c>
       <c r="G61">
-        <v>47222671.95</v>
+        <v>52804838.5</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -2557,19 +2557,19 @@
         <v>158</v>
       </c>
       <c r="E62">
-        <v>264309178.14</v>
+        <v>282418757.16</v>
       </c>
       <c r="F62">
-        <v>214905790.39</v>
+        <v>221607635.39</v>
       </c>
       <c r="G62">
-        <v>198070418.99</v>
+        <v>206479913.09</v>
       </c>
       <c r="H62">
-        <v>199241931.12</v>
+        <v>199255762.91</v>
       </c>
       <c r="I62">
-        <v>194560643.74</v>
+        <v>194574267.24</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -2586,19 +2586,19 @@
         <v>159</v>
       </c>
       <c r="E63">
-        <v>74330418.38</v>
+        <v>81036959.81</v>
       </c>
       <c r="F63">
-        <v>56439020.41</v>
+        <v>63137838.45</v>
       </c>
       <c r="G63">
-        <v>51058502.79</v>
+        <v>51461795.07</v>
       </c>
       <c r="H63">
-        <v>35587470.8</v>
+        <v>35607662.47</v>
       </c>
       <c r="I63">
-        <v>54117902.32</v>
+        <v>54176450.61</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -2615,13 +2615,13 @@
         <v>160</v>
       </c>
       <c r="E64">
-        <v>11632286.88</v>
+        <v>14547860.45</v>
       </c>
       <c r="F64">
-        <v>9287887.23</v>
+        <v>9316494.17</v>
       </c>
       <c r="G64">
-        <v>8743906.619999999</v>
+        <v>8770199.68</v>
       </c>
       <c r="H64">
         <v>1960878.57</v>
@@ -2647,10 +2647,10 @@
         <v>731805.9300000001</v>
       </c>
       <c r="F65">
-        <v>587546.46</v>
+        <v>688119.66</v>
       </c>
       <c r="G65">
-        <v>510301.8</v>
+        <v>595570.3</v>
       </c>
       <c r="H65">
         <v>34744.58</v>
@@ -2693,13 +2693,13 @@
         <v>163</v>
       </c>
       <c r="E67">
-        <v>1475088.13</v>
+        <v>1590232.88</v>
       </c>
       <c r="F67">
-        <v>1354242.36</v>
+        <v>1379218.54</v>
       </c>
       <c r="G67">
-        <v>1252508.54</v>
+        <v>1277057.45</v>
       </c>
       <c r="H67">
         <v>94595.71000000001</v>
@@ -2722,16 +2722,16 @@
         <v>164</v>
       </c>
       <c r="E68">
-        <v>266762466.33</v>
+        <v>274808268.87</v>
       </c>
       <c r="F68">
-        <v>203836961.33</v>
+        <v>210959212.79</v>
       </c>
       <c r="G68">
-        <v>186569321.48</v>
+        <v>188764799.78</v>
       </c>
       <c r="H68">
-        <v>55051157.61</v>
+        <v>55083811.23</v>
       </c>
       <c r="I68">
         <v>60641733.47</v>
@@ -2751,19 +2751,19 @@
         <v>165</v>
       </c>
       <c r="E69">
-        <v>310728351.95</v>
+        <v>310602127.4</v>
       </c>
       <c r="F69">
-        <v>233246913.17</v>
+        <v>244723627.7</v>
       </c>
       <c r="G69">
-        <v>202940330.5</v>
+        <v>213731917.05</v>
       </c>
       <c r="H69">
-        <v>91876339.38</v>
+        <v>91892374.91</v>
       </c>
       <c r="I69">
-        <v>88839854.8</v>
+        <v>88843247.72</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -2780,19 +2780,19 @@
         <v>166</v>
       </c>
       <c r="E70">
-        <v>559532373.97</v>
+        <v>570518571.86</v>
       </c>
       <c r="F70">
-        <v>396071508.92</v>
+        <v>343921850.89</v>
       </c>
       <c r="G70">
-        <v>275084313.9</v>
+        <v>289478414.27</v>
       </c>
       <c r="H70">
-        <v>260924471.54</v>
+        <v>262532808.59</v>
       </c>
       <c r="I70">
-        <v>267428072.35</v>
+        <v>269081449.98</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -2812,10 +2812,10 @@
         <v>1129934.24</v>
       </c>
       <c r="F71">
-        <v>1102441.65</v>
+        <v>1102750.89</v>
       </c>
       <c r="G71">
-        <v>984963.39</v>
+        <v>985257.79</v>
       </c>
       <c r="H71">
         <v>225243.01</v>
@@ -2838,13 +2838,13 @@
         <v>168</v>
       </c>
       <c r="E72">
-        <v>62658228.81</v>
+        <v>62937013.1</v>
       </c>
       <c r="F72">
-        <v>40917682.44</v>
+        <v>42130376.02</v>
       </c>
       <c r="G72">
-        <v>39248919.45</v>
+        <v>40440359.42</v>
       </c>
       <c r="H72">
         <v>19576645.24</v>
@@ -2867,16 +2867,16 @@
         <v>169</v>
       </c>
       <c r="E73">
-        <v>1951588.53</v>
+        <v>2018267.88</v>
       </c>
       <c r="F73">
-        <v>1854616.61</v>
+        <v>1865993.32</v>
       </c>
       <c r="G73">
-        <v>1478589.79</v>
+        <v>1642919.03</v>
       </c>
       <c r="H73">
-        <v>34378.25</v>
+        <v>54883.85</v>
       </c>
       <c r="I73">
         <v>34378.25</v>
@@ -2896,19 +2896,19 @@
         <v>170</v>
       </c>
       <c r="E74">
-        <v>124760964.67</v>
+        <v>124874011.61</v>
       </c>
       <c r="F74">
-        <v>70394879.22</v>
+        <v>71993224.29000001</v>
       </c>
       <c r="G74">
-        <v>66048632.08</v>
+        <v>66889632.2</v>
       </c>
       <c r="H74">
-        <v>68490777.18000001</v>
+        <v>69384239.06999999</v>
       </c>
       <c r="I74">
-        <v>64895141.78</v>
+        <v>65198612.56</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -2925,13 +2925,13 @@
         <v>171</v>
       </c>
       <c r="E75">
-        <v>23091951.84</v>
+        <v>23093980.28</v>
       </c>
       <c r="F75">
-        <v>17873715.48</v>
+        <v>18015810.84</v>
       </c>
       <c r="G75">
-        <v>14545966.69</v>
+        <v>14568798.59</v>
       </c>
       <c r="H75">
         <v>674995.91</v>
@@ -2954,19 +2954,19 @@
         <v>172</v>
       </c>
       <c r="E76">
-        <v>244424975.99</v>
+        <v>244533181.99</v>
       </c>
       <c r="F76">
-        <v>13994305.33</v>
+        <v>15204711.72</v>
       </c>
       <c r="G76">
-        <v>12478206.3</v>
+        <v>13523031.56</v>
       </c>
       <c r="H76">
-        <v>58510718.79</v>
+        <v>58838498.79</v>
       </c>
       <c r="I76">
-        <v>55214148.64</v>
+        <v>55354211.2</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -2983,19 +2983,19 @@
         <v>173</v>
       </c>
       <c r="E77">
-        <v>29191047.41</v>
+        <v>29957633.64</v>
       </c>
       <c r="F77">
-        <v>24903655.77</v>
+        <v>25603700.43</v>
       </c>
       <c r="G77">
-        <v>22839531.14</v>
+        <v>22933595.45</v>
       </c>
       <c r="H77">
         <v>19722571.84</v>
       </c>
       <c r="I77">
-        <v>30501377.48</v>
+        <v>30796241.68</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -3012,19 +3012,19 @@
         <v>174</v>
       </c>
       <c r="E78">
-        <v>1123312635.13</v>
+        <v>1169790508.99</v>
       </c>
       <c r="F78">
-        <v>854784510.9</v>
+        <v>874837049.1</v>
       </c>
       <c r="G78">
-        <v>826336317.21</v>
+        <v>843880412.99</v>
       </c>
       <c r="H78">
-        <v>161989712.75</v>
+        <v>162002254.83</v>
       </c>
       <c r="I78">
-        <v>358867940.53</v>
+        <v>358958251.22</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -3041,19 +3041,19 @@
         <v>175</v>
       </c>
       <c r="E79">
-        <v>202041161.36</v>
+        <v>204847855.61</v>
       </c>
       <c r="F79">
-        <v>160334112.92</v>
+        <v>164881735.99</v>
       </c>
       <c r="G79">
-        <v>134266309.14</v>
+        <v>137552124.84</v>
       </c>
       <c r="H79">
-        <v>63256021.9</v>
+        <v>63400309.9</v>
       </c>
       <c r="I79">
-        <v>67834742.25</v>
+        <v>68000531.79000001</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -3070,13 +3070,13 @@
         <v>176</v>
       </c>
       <c r="E80">
-        <v>36883900.73</v>
+        <v>36903795.73</v>
       </c>
       <c r="F80">
-        <v>33272577.59</v>
+        <v>33631027.12</v>
       </c>
       <c r="G80">
-        <v>28967333.12</v>
+        <v>29077455.15</v>
       </c>
       <c r="H80">
         <v>4983225.57</v>
@@ -3099,19 +3099,19 @@
         <v>177</v>
       </c>
       <c r="E81">
-        <v>58640469.78</v>
+        <v>63489815.97</v>
       </c>
       <c r="F81">
-        <v>36565561.71</v>
+        <v>36846441.82</v>
       </c>
       <c r="G81">
-        <v>33821449.89</v>
+        <v>34396627.51</v>
       </c>
       <c r="H81">
-        <v>96263747.28</v>
+        <v>96470027.48</v>
       </c>
       <c r="I81">
-        <v>152910770.7</v>
+        <v>153345393.65</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -3128,19 +3128,19 @@
         <v>178</v>
       </c>
       <c r="E82">
-        <v>699542763.37</v>
+        <v>728633725.63</v>
       </c>
       <c r="F82">
-        <v>513029492.18</v>
+        <v>534264651.97</v>
       </c>
       <c r="G82">
-        <v>483109992.42</v>
+        <v>498384633.08</v>
       </c>
       <c r="H82">
-        <v>157600145.61</v>
+        <v>158041931.06</v>
       </c>
       <c r="I82">
-        <v>158556440.29</v>
+        <v>158938463.9</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -3157,13 +3157,13 @@
         <v>179</v>
       </c>
       <c r="E83">
-        <v>36832065.82</v>
+        <v>38314729.8</v>
       </c>
       <c r="F83">
-        <v>35429728.06</v>
+        <v>35795121.98</v>
       </c>
       <c r="G83">
-        <v>27121135.84</v>
+        <v>31711904.78</v>
       </c>
       <c r="H83">
         <v>4788587.37</v>
@@ -3186,19 +3186,19 @@
         <v>180</v>
       </c>
       <c r="E84">
-        <v>286387941.34</v>
+        <v>315680141.19</v>
       </c>
       <c r="F84">
-        <v>240724500.19</v>
+        <v>248311482.32</v>
       </c>
       <c r="G84">
-        <v>217780517.05</v>
+        <v>227648047.88</v>
       </c>
       <c r="H84">
-        <v>75127332</v>
+        <v>75127474.78</v>
       </c>
       <c r="I84">
-        <v>100674914.42</v>
+        <v>100675041.99</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -3215,13 +3215,13 @@
         <v>181</v>
       </c>
       <c r="E85">
-        <v>109983811.04</v>
+        <v>111687206.56</v>
       </c>
       <c r="F85">
-        <v>81954107.45999999</v>
+        <v>85310057.42</v>
       </c>
       <c r="G85">
-        <v>69479979.03</v>
+        <v>71150296.09</v>
       </c>
       <c r="H85">
         <v>34371578.38</v>
@@ -3244,19 +3244,19 @@
         <v>182</v>
       </c>
       <c r="E86">
-        <v>11697041.21</v>
+        <v>11905416.5</v>
       </c>
       <c r="F86">
-        <v>10030599.88</v>
+        <v>10162086.46</v>
       </c>
       <c r="G86">
-        <v>8928663.029999999</v>
+        <v>9004948.060000001</v>
       </c>
       <c r="H86">
-        <v>5521109.94</v>
+        <v>5551396.54</v>
       </c>
       <c r="I86">
-        <v>5326919.47</v>
+        <v>5352360.2</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -3273,10 +3273,10 @@
         <v>183</v>
       </c>
       <c r="E87">
-        <v>6040468.66</v>
+        <v>6073223.7</v>
       </c>
       <c r="F87">
-        <v>5569365.56</v>
+        <v>5699055.76</v>
       </c>
       <c r="G87">
         <v>4030449.14</v>
@@ -3302,13 +3302,13 @@
         <v>184</v>
       </c>
       <c r="E88">
-        <v>75679642.8</v>
+        <v>82596645.39</v>
       </c>
       <c r="F88">
-        <v>53289940.68</v>
+        <v>55307879.85</v>
       </c>
       <c r="G88">
-        <v>47724632.71</v>
+        <v>49340867.02</v>
       </c>
       <c r="H88">
         <v>20927257.25</v>
@@ -3331,19 +3331,19 @@
         <v>185</v>
       </c>
       <c r="E89">
-        <v>66179318.45</v>
+        <v>67503299</v>
       </c>
       <c r="F89">
-        <v>45405682.15</v>
+        <v>48795706.75</v>
       </c>
       <c r="G89">
-        <v>40729380.6</v>
+        <v>43599549.22</v>
       </c>
       <c r="H89">
-        <v>26399033.76</v>
+        <v>26411726.73</v>
       </c>
       <c r="I89">
-        <v>24362187.11</v>
+        <v>24373712.33</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -3360,13 +3360,13 @@
         <v>186</v>
       </c>
       <c r="E90">
-        <v>2621464.07</v>
+        <v>3378848.18</v>
       </c>
       <c r="F90">
-        <v>2358341.87</v>
+        <v>2369539.24</v>
       </c>
       <c r="G90">
-        <v>2068656.31</v>
+        <v>2079853.68</v>
       </c>
       <c r="H90">
         <v>294468.9</v>

--- a/upload/orgao2026.xlsx
+++ b/upload/orgao2026.xlsx
@@ -493,16 +493,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>25533153.3</v>
+        <v>26180519.2</v>
       </c>
       <c r="F2" t="n">
-        <v>19889718.88</v>
+        <v>20512035.12</v>
       </c>
       <c r="G2" t="n">
-        <v>17665425.89</v>
+        <v>18223555.6</v>
       </c>
       <c r="H2" t="n">
-        <v>2907037.16</v>
+        <v>2940314.6</v>
       </c>
       <c r="I2" t="n">
         <v>216994912.01</v>
@@ -559,13 +559,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>230972763</v>
+        <v>229005752.9</v>
       </c>
       <c r="F4" t="n">
-        <v>145446237.58</v>
+        <v>149079561.99</v>
       </c>
       <c r="G4" t="n">
-        <v>131961229.77</v>
+        <v>135837815.83</v>
       </c>
       <c r="H4" t="n">
         <v>36533257.42</v>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2719326.48</v>
+        <v>2719326.31</v>
       </c>
       <c r="F6" t="n">
         <v>1842937.75</v>
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>26490821.19</v>
+        <v>32914761.2</v>
       </c>
       <c r="F7" t="n">
-        <v>22186764.99</v>
+        <v>22908351.09</v>
       </c>
       <c r="G7" t="n">
         <v>19967540.03</v>
@@ -691,19 +691,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>91940650.03</v>
+        <v>93175865.84999999</v>
       </c>
       <c r="F8" t="n">
-        <v>42677576.1</v>
+        <v>43832968.28</v>
       </c>
       <c r="G8" t="n">
-        <v>38124298.97</v>
+        <v>39926244.16</v>
       </c>
       <c r="H8" t="n">
-        <v>54349318.78</v>
+        <v>54387100.16</v>
       </c>
       <c r="I8" t="n">
-        <v>53903825.43</v>
+        <v>53917061.51</v>
       </c>
     </row>
     <row r="9">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3748635.26</v>
+        <v>3752622.91</v>
       </c>
       <c r="F9" t="n">
-        <v>3014149.24</v>
+        <v>3014366.37</v>
       </c>
       <c r="G9" t="n">
-        <v>2907624.42</v>
+        <v>2907831.13</v>
       </c>
       <c r="H9" t="n">
         <v>1345976.77</v>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103279231.81</v>
+        <v>103941035.94</v>
       </c>
       <c r="F10" t="n">
-        <v>93250102.59999999</v>
+        <v>93956768</v>
       </c>
       <c r="G10" t="n">
-        <v>83340203.19</v>
+        <v>83828243.01000001</v>
       </c>
       <c r="H10" t="n">
         <v>14925708.98</v>
@@ -790,19 +790,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2038800542.36</v>
+        <v>2065279256.28</v>
       </c>
       <c r="F11" t="n">
-        <v>1053397621.41</v>
+        <v>1121480840.88</v>
       </c>
       <c r="G11" t="n">
-        <v>1003135474.56</v>
+        <v>1062981682.25</v>
       </c>
       <c r="H11" t="n">
-        <v>358870997.55</v>
+        <v>363303617.81</v>
       </c>
       <c r="I11" t="n">
-        <v>366485316.8</v>
+        <v>366507612.71</v>
       </c>
     </row>
     <row r="12">
@@ -823,13 +823,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53963675.51</v>
+        <v>53966936.56</v>
       </c>
       <c r="F12" t="n">
-        <v>45811799.96</v>
+        <v>45927490.19</v>
       </c>
       <c r="G12" t="n">
-        <v>43784142.05</v>
+        <v>43895626.6</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -888,7 +888,7 @@
         <v>2889353.5</v>
       </c>
       <c r="F14" t="n">
-        <v>953326.64</v>
+        <v>1141697.01</v>
       </c>
       <c r="G14" t="n">
         <v>877088.74</v>
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9651387.02</v>
+        <v>9652526.119999999</v>
       </c>
       <c r="F19" t="n">
         <v>5628137.76</v>
       </c>
       <c r="G19" t="n">
-        <v>5035997.15</v>
+        <v>5150756.79</v>
       </c>
       <c r="H19" t="n">
         <v>1045788.75</v>
@@ -1094,7 +1094,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1103756.08</v>
+        <v>1143457.08</v>
       </c>
       <c r="F21" t="n">
         <v>1047237.79</v>
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>22161481.49</v>
+        <v>23627681.96</v>
       </c>
       <c r="F22" t="n">
-        <v>19512626.06</v>
+        <v>19584224.36</v>
       </c>
       <c r="G22" t="n">
-        <v>17182438.87</v>
+        <v>17463017.73</v>
       </c>
       <c r="H22" t="n">
         <v>4351124.84</v>
@@ -1160,13 +1160,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>11357755.93</v>
+        <v>11414800.67</v>
       </c>
       <c r="F23" t="n">
         <v>10540330.65</v>
       </c>
       <c r="G23" t="n">
-        <v>9324429.279999999</v>
+        <v>9332977.02</v>
       </c>
       <c r="H23" t="n">
         <v>1776239.78</v>
@@ -1226,13 +1226,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>23538880.27</v>
+        <v>27167898.27</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>613730.08</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>496938.88</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>14012749.86</v>
+        <v>14463249.86</v>
       </c>
       <c r="F26" t="n">
-        <v>5170519.09</v>
+        <v>5248183.09</v>
       </c>
       <c r="G26" t="n">
-        <v>5092533</v>
+        <v>5190047</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -1284,19 +1284,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>12235265.34</v>
+        <v>12293471.66</v>
       </c>
       <c r="F27" t="n">
-        <v>11628307.35</v>
+        <v>11678971.07</v>
       </c>
       <c r="G27" t="n">
-        <v>9967570.34</v>
+        <v>10364668</v>
       </c>
       <c r="H27" t="n">
         <v>1102594.36</v>
       </c>
       <c r="I27" t="n">
-        <v>1012619.95</v>
+        <v>1012620.56</v>
       </c>
     </row>
     <row r="28">
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>10126464.69</v>
+        <v>10184475.69</v>
       </c>
       <c r="F28" t="n">
-        <v>8513424.369999999</v>
+        <v>8521028.27</v>
       </c>
       <c r="G28" t="n">
-        <v>7064043.54</v>
+        <v>7494478.64</v>
       </c>
       <c r="H28" t="n">
-        <v>1547396.65</v>
+        <v>1548259.79</v>
       </c>
       <c r="I28" t="n">
         <v>2024584.08</v>
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>18965012.24</v>
+        <v>19014855.83</v>
       </c>
       <c r="F30" t="n">
-        <v>2244595.52</v>
+        <v>2542240.46</v>
       </c>
       <c r="G30" t="n">
-        <v>2183755.8</v>
+        <v>2306299.67</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -1463,10 +1463,10 @@
         <v>16152446.21</v>
       </c>
       <c r="F33" t="n">
-        <v>10978430</v>
+        <v>10999861.97</v>
       </c>
       <c r="G33" t="n">
-        <v>9835381.050000001</v>
+        <v>9842763.15</v>
       </c>
       <c r="H33" t="n">
         <v>33790513.37</v>
@@ -1493,19 +1493,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1734944459.34</v>
+        <v>1783467244.04</v>
       </c>
       <c r="F34" t="n">
-        <v>1394143212.86</v>
+        <v>1453657922.46</v>
       </c>
       <c r="G34" t="n">
-        <v>1204590142.13</v>
+        <v>1253525282.35</v>
       </c>
       <c r="H34" t="n">
-        <v>268677608.87</v>
+        <v>268690115.87</v>
       </c>
       <c r="I34" t="n">
-        <v>250021582.88</v>
+        <v>250031525.01</v>
       </c>
     </row>
     <row r="35">
@@ -1526,19 +1526,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1114860005.35</v>
+        <v>1110280684.32</v>
       </c>
       <c r="F35" t="n">
-        <v>730533464.25</v>
+        <v>752981907.08</v>
       </c>
       <c r="G35" t="n">
-        <v>664463730.74</v>
+        <v>689447840.0599999</v>
       </c>
       <c r="H35" t="n">
-        <v>597650607.98</v>
+        <v>598559947.12</v>
       </c>
       <c r="I35" t="n">
-        <v>1244721096.44</v>
+        <v>1245193832.55</v>
       </c>
     </row>
     <row r="36">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53540678</v>
+        <v>53656639.82</v>
       </c>
       <c r="F36" t="n">
-        <v>18957782.75</v>
+        <v>19536605.86</v>
       </c>
       <c r="G36" t="n">
-        <v>14929325.63</v>
+        <v>17586419.01</v>
       </c>
       <c r="H36" t="n">
-        <v>46198596.32</v>
+        <v>47509837.34</v>
       </c>
       <c r="I36" t="n">
-        <v>52179185.66</v>
+        <v>52313631.03</v>
       </c>
     </row>
     <row r="37">
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>413829.9</v>
+        <v>422250.64</v>
       </c>
       <c r="F37" t="n">
         <v>374019.78</v>
@@ -1652,13 +1652,13 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>23958043.39</v>
+        <v>24444034.89</v>
       </c>
       <c r="F39" t="n">
-        <v>12712194.54</v>
+        <v>12748065.37</v>
       </c>
       <c r="G39" t="n">
-        <v>12053396.3</v>
+        <v>12169558.05</v>
       </c>
       <c r="H39" t="n">
         <v>2243300.48</v>
@@ -1685,19 +1685,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>580263686.9299999</v>
+        <v>586543234.62</v>
       </c>
       <c r="F40" t="n">
-        <v>485101681.04</v>
+        <v>494743533.91</v>
       </c>
       <c r="G40" t="n">
-        <v>433822067.27</v>
+        <v>446823619.89</v>
       </c>
       <c r="H40" t="n">
-        <v>100952280.91</v>
+        <v>101739393.73</v>
       </c>
       <c r="I40" t="n">
-        <v>101490775.1</v>
+        <v>101567592.54</v>
       </c>
     </row>
     <row r="41">
@@ -1778,16 +1778,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>11418882.97</v>
+        <v>11436667.94</v>
       </c>
       <c r="F43" t="n">
-        <v>8200977.96</v>
+        <v>8211029.03</v>
       </c>
       <c r="G43" t="n">
-        <v>7170624.99</v>
+        <v>7186877.68</v>
       </c>
       <c r="H43" t="n">
-        <v>2764442.66</v>
+        <v>2785558.25</v>
       </c>
       <c r="I43" t="n">
         <v>2572518.83</v>
@@ -1847,13 +1847,13 @@
         <v>613399284.2</v>
       </c>
       <c r="F45" t="n">
-        <v>292985786.82</v>
+        <v>293541070.01</v>
       </c>
       <c r="G45" t="n">
-        <v>268069581.77</v>
+        <v>268057326.3</v>
       </c>
       <c r="H45" t="n">
-        <v>38776739.66</v>
+        <v>41324765.01</v>
       </c>
       <c r="I45" t="n">
         <v>89063165.06</v>
@@ -1877,7 +1877,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2098871.12</v>
+        <v>2117707</v>
       </c>
       <c r="F46" t="n">
         <v>1246331.28</v>
@@ -1886,7 +1886,7 @@
         <v>1123142.41</v>
       </c>
       <c r="H46" t="n">
-        <v>179553.95</v>
+        <v>180733.15</v>
       </c>
       <c r="I46" t="n">
         <v>201015.49</v>
@@ -1964,13 +1964,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>387189983.41</v>
+        <v>380953405.81</v>
       </c>
       <c r="F49" t="n">
-        <v>207900818.19</v>
+        <v>208813609.97</v>
       </c>
       <c r="G49" t="n">
-        <v>154038841.93</v>
+        <v>158476748.45</v>
       </c>
       <c r="H49" t="n">
         <v>136601196.75</v>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>16911292.63</v>
+        <v>16959992.63</v>
       </c>
       <c r="F50" t="n">
         <v>15773809.96</v>
@@ -2009,7 +2009,7 @@
         <v>20055028.48</v>
       </c>
       <c r="I50" t="n">
-        <v>21400403.18</v>
+        <v>21402011.05</v>
       </c>
     </row>
     <row r="51">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>120466805.78</v>
+        <v>120876397.54</v>
       </c>
       <c r="F51" t="n">
-        <v>75566197.94</v>
+        <v>76943466.92</v>
       </c>
       <c r="G51" t="n">
-        <v>71128144.41</v>
+        <v>72437784.33</v>
       </c>
       <c r="H51" t="n">
         <v>18617499.53</v>
@@ -2063,13 +2063,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>49271405.01</v>
+        <v>49810164.18</v>
       </c>
       <c r="F52" t="n">
-        <v>25109617.13</v>
+        <v>25161729.16</v>
       </c>
       <c r="G52" t="n">
-        <v>23076565.08</v>
+        <v>23200144.77</v>
       </c>
       <c r="H52" t="n">
         <v>12470050.72</v>
@@ -2123,16 +2123,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>160163599.55</v>
+        <v>161849202.46</v>
       </c>
       <c r="F54" t="n">
-        <v>134018309.26</v>
+        <v>137927830.4</v>
       </c>
       <c r="G54" t="n">
-        <v>121095952.81</v>
+        <v>122238811.71</v>
       </c>
       <c r="H54" t="n">
-        <v>24667775.39</v>
+        <v>24674329.49</v>
       </c>
       <c r="I54" t="n">
         <v>27482989.13</v>
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>39214584.1</v>
+        <v>39157746.85</v>
       </c>
       <c r="F55" t="n">
-        <v>27015714.76</v>
+        <v>27800907.9</v>
       </c>
       <c r="G55" t="n">
-        <v>26300577.2</v>
+        <v>26465202.42</v>
       </c>
       <c r="H55" t="n">
         <v>22680133.16</v>
@@ -2189,13 +2189,13 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>55151701.19</v>
+        <v>55672847.35</v>
       </c>
       <c r="F56" t="n">
-        <v>48476141.67</v>
+        <v>48718600.73</v>
       </c>
       <c r="G56" t="n">
-        <v>40053127.11</v>
+        <v>41585487.3</v>
       </c>
       <c r="H56" t="n">
         <v>8927627.439999999</v>
@@ -2222,13 +2222,13 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6608515.65</v>
+        <v>6609340.05</v>
       </c>
       <c r="F57" t="n">
-        <v>4507684.04</v>
+        <v>4547114.91</v>
       </c>
       <c r="G57" t="n">
-        <v>4005581.94</v>
+        <v>4044932.46</v>
       </c>
       <c r="H57" t="n">
         <v>675363.28</v>
@@ -2255,13 +2255,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>7510126.23</v>
+        <v>7573021.84</v>
       </c>
       <c r="F58" t="n">
-        <v>6650102.67</v>
+        <v>6795315.76</v>
       </c>
       <c r="G58" t="n">
-        <v>6286770.19</v>
+        <v>6364172.4</v>
       </c>
       <c r="H58" t="n">
         <v>11029049.85</v>
@@ -2288,13 +2288,13 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>18231821.42</v>
+        <v>19645187.18</v>
       </c>
       <c r="F59" t="n">
-        <v>10611633.61</v>
+        <v>10715783.95</v>
       </c>
       <c r="G59" t="n">
-        <v>9859815.74</v>
+        <v>9942395.07</v>
       </c>
       <c r="H59" t="n">
         <v>5263133.99</v>
@@ -2321,13 +2321,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>12381552.02</v>
+        <v>12398378.78</v>
       </c>
       <c r="F60" t="n">
-        <v>12030163.75</v>
+        <v>12056235.26</v>
       </c>
       <c r="G60" t="n">
-        <v>10643985.33</v>
+        <v>10669017.17</v>
       </c>
       <c r="H60" t="n">
         <v>1332496.42</v>
@@ -2383,19 +2383,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>298917362.99</v>
+        <v>303422842.59</v>
       </c>
       <c r="F62" t="n">
-        <v>228456013.9</v>
+        <v>233358714.9</v>
       </c>
       <c r="G62" t="n">
-        <v>211744366.53</v>
+        <v>214108646.84</v>
       </c>
       <c r="H62" t="n">
-        <v>199256579.48</v>
+        <v>199273348.97</v>
       </c>
       <c r="I62" t="n">
-        <v>194575083.81</v>
+        <v>194590553.39</v>
       </c>
     </row>
     <row r="63">
@@ -2416,13 +2416,13 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>81269821.17</v>
+        <v>91021149.92</v>
       </c>
       <c r="F63" t="n">
-        <v>63664209.15</v>
+        <v>64380271.45</v>
       </c>
       <c r="G63" t="n">
-        <v>58209235.59</v>
+        <v>58650463.47</v>
       </c>
       <c r="H63" t="n">
         <v>35607662.46</v>
@@ -2449,13 +2449,13 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>14547857.76</v>
+        <v>15109881.49</v>
       </c>
       <c r="F64" t="n">
-        <v>9349948.050000001</v>
+        <v>10294067.79</v>
       </c>
       <c r="G64" t="n">
-        <v>8804736.699999999</v>
+        <v>9679021.09</v>
       </c>
       <c r="H64" t="n">
         <v>1960878.57</v>
@@ -2482,13 +2482,13 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>731678.9399999999</v>
+        <v>734812.8100000001</v>
       </c>
       <c r="F65" t="n">
         <v>692014.03</v>
       </c>
       <c r="G65" t="n">
-        <v>595570.3</v>
+        <v>599464.67</v>
       </c>
       <c r="H65" t="n">
         <v>34744.58</v>
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1590232.88</v>
+        <v>1603130.94</v>
       </c>
       <c r="F67" t="n">
-        <v>1478395.64</v>
+        <v>1478735.34</v>
       </c>
       <c r="G67" t="n">
-        <v>1361454.46</v>
+        <v>1361777.85</v>
       </c>
       <c r="H67" t="n">
         <v>94595.71000000001</v>
@@ -2575,19 +2575,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>278030910.78</v>
+        <v>292811811.6</v>
       </c>
       <c r="F68" t="n">
-        <v>215225593.89</v>
+        <v>220400711.08</v>
       </c>
       <c r="G68" t="n">
-        <v>198168285.07</v>
+        <v>203123243.49</v>
       </c>
       <c r="H68" t="n">
-        <v>55143693.75</v>
+        <v>55170835.14</v>
       </c>
       <c r="I68" t="n">
-        <v>62260127.09</v>
+        <v>62277879.89</v>
       </c>
     </row>
     <row r="69">
@@ -2608,19 +2608,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>312788429.69</v>
+        <v>313893594.97</v>
       </c>
       <c r="F69" t="n">
-        <v>251518361.33</v>
+        <v>254552403.39</v>
       </c>
       <c r="G69" t="n">
-        <v>219060290.58</v>
+        <v>221598057.66</v>
       </c>
       <c r="H69" t="n">
-        <v>94234834.41</v>
+        <v>94439667.73</v>
       </c>
       <c r="I69" t="n">
-        <v>91078805.78</v>
+        <v>91215960.83</v>
       </c>
     </row>
     <row r="70">
@@ -2641,19 +2641,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>588103852.64</v>
+        <v>597844574.78</v>
       </c>
       <c r="F70" t="n">
-        <v>367806439.09</v>
+        <v>372282357.56</v>
       </c>
       <c r="G70" t="n">
-        <v>300751947.4</v>
+        <v>336660804.07</v>
       </c>
       <c r="H70" t="n">
         <v>263021865.1</v>
       </c>
       <c r="I70" t="n">
-        <v>269136440.55</v>
+        <v>271523413.35</v>
       </c>
     </row>
     <row r="71">
@@ -2707,13 +2707,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>66168510.9</v>
+        <v>66213722.8</v>
       </c>
       <c r="F72" t="n">
-        <v>42391729.72</v>
+        <v>43220616.29</v>
       </c>
       <c r="G72" t="n">
-        <v>40690375.95</v>
+        <v>41468872.19</v>
       </c>
       <c r="H72" t="n">
         <v>19576645.24</v>
@@ -2740,13 +2740,13 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2048442.91</v>
+        <v>2186529.64</v>
       </c>
       <c r="F73" t="n">
-        <v>1870390.88</v>
+        <v>1873679.76</v>
       </c>
       <c r="G73" t="n">
-        <v>1650351.13</v>
+        <v>1653551.66</v>
       </c>
       <c r="H73" t="n">
         <v>54883.85</v>
@@ -2773,19 +2773,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>114681643.76</v>
+        <v>114672240.69</v>
       </c>
       <c r="F74" t="n">
-        <v>73958420.98999999</v>
+        <v>74461445.66</v>
       </c>
       <c r="G74" t="n">
-        <v>70125739.88</v>
+        <v>70416642.48</v>
       </c>
       <c r="H74" t="n">
-        <v>69457346.64</v>
+        <v>69464857.84999999</v>
       </c>
       <c r="I74" t="n">
-        <v>65992388.27</v>
+        <v>66003730.8</v>
       </c>
     </row>
     <row r="75">
@@ -2806,13 +2806,13 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>23972880.28</v>
+        <v>24999507.75</v>
       </c>
       <c r="F75" t="n">
-        <v>18026802.26</v>
+        <v>18047703.16</v>
       </c>
       <c r="G75" t="n">
-        <v>14646165.4</v>
+        <v>15067804.93</v>
       </c>
       <c r="H75" t="n">
         <v>674995.91</v>
@@ -2839,19 +2839,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>244983181.99</v>
+        <v>245379570.61</v>
       </c>
       <c r="F76" t="n">
-        <v>15536458.8</v>
+        <v>15818729.51</v>
       </c>
       <c r="G76" t="n">
-        <v>13851051.62</v>
+        <v>13851609.43</v>
       </c>
       <c r="H76" t="n">
-        <v>58838498.79</v>
+        <v>64034547.31</v>
       </c>
       <c r="I76" t="n">
-        <v>55521743.2</v>
+        <v>55863962.72</v>
       </c>
     </row>
     <row r="77">
@@ -2872,19 +2872,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>30533525.37</v>
+        <v>34316162.75</v>
       </c>
       <c r="F77" t="n">
-        <v>27135846.54</v>
+        <v>27201862.23</v>
       </c>
       <c r="G77" t="n">
-        <v>24105088.77</v>
+        <v>24534634.81</v>
       </c>
       <c r="H77" t="n">
-        <v>19969200.64</v>
+        <v>20223535.76</v>
       </c>
       <c r="I77" t="n">
-        <v>31039910.96</v>
+        <v>31276916.62</v>
       </c>
     </row>
     <row r="78">
@@ -2905,19 +2905,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1187985200.81</v>
+        <v>1197947340.58</v>
       </c>
       <c r="F78" t="n">
-        <v>896094383.25</v>
+        <v>909520049.8099999</v>
       </c>
       <c r="G78" t="n">
-        <v>865728239.47</v>
+        <v>880055944.52</v>
       </c>
       <c r="H78" t="n">
-        <v>162124026.63</v>
+        <v>162244540.43</v>
       </c>
       <c r="I78" t="n">
-        <v>359145936.26</v>
+        <v>359229123.45</v>
       </c>
     </row>
     <row r="79">
@@ -2938,19 +2938,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>213598412.86</v>
+        <v>224073140.11</v>
       </c>
       <c r="F79" t="n">
-        <v>166030975.99</v>
+        <v>166857964.81</v>
       </c>
       <c r="G79" t="n">
-        <v>140091789.17</v>
+        <v>149167924.32</v>
       </c>
       <c r="H79" t="n">
-        <v>63576653.66</v>
+        <v>64268556.04</v>
       </c>
       <c r="I79" t="n">
-        <v>68000531.79000001</v>
+        <v>68710006.3</v>
       </c>
     </row>
     <row r="80">
@@ -2971,13 +2971,13 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>36930575.73</v>
+        <v>37580272.91</v>
       </c>
       <c r="F80" t="n">
-        <v>33637807.73</v>
+        <v>34167433.08</v>
       </c>
       <c r="G80" t="n">
-        <v>30708116.91</v>
+        <v>31235366</v>
       </c>
       <c r="H80" t="n">
         <v>4983225.57</v>
@@ -3004,19 +3004,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>66946935.97</v>
+        <v>69877282.08</v>
       </c>
       <c r="F81" t="n">
-        <v>37445955.07</v>
+        <v>39494432.08</v>
       </c>
       <c r="G81" t="n">
-        <v>34762519.37</v>
+        <v>36869606.7</v>
       </c>
       <c r="H81" t="n">
-        <v>97642595.40000001</v>
+        <v>98521871.51000001</v>
       </c>
       <c r="I81" t="n">
-        <v>154380717.81</v>
+        <v>154592131.43</v>
       </c>
     </row>
     <row r="82">
@@ -3037,19 +3037,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>735946257.4299999</v>
+        <v>758800792.6900001</v>
       </c>
       <c r="F82" t="n">
-        <v>555693482.29</v>
+        <v>568164811.52</v>
       </c>
       <c r="G82" t="n">
-        <v>522637389.07</v>
+        <v>536995211.64</v>
       </c>
       <c r="H82" t="n">
-        <v>158917313.39</v>
+        <v>159264201.46</v>
       </c>
       <c r="I82" t="n">
-        <v>168194218.55</v>
+        <v>169625754.61</v>
       </c>
     </row>
     <row r="83">
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>38828559.11</v>
+        <v>39233294.54</v>
       </c>
       <c r="F83" t="n">
-        <v>36962656.52</v>
+        <v>36973165.36</v>
       </c>
       <c r="G83" t="n">
-        <v>32781371.79</v>
+        <v>33033708.51</v>
       </c>
       <c r="H83" t="n">
         <v>5083500.33</v>
@@ -3103,19 +3103,19 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>326877169.7</v>
+        <v>328502057.45</v>
       </c>
       <c r="F84" t="n">
-        <v>252508619.48</v>
+        <v>253813161.37</v>
       </c>
       <c r="G84" t="n">
-        <v>232092086.07</v>
+        <v>232863212.28</v>
       </c>
       <c r="H84" t="n">
-        <v>75254651.75</v>
+        <v>76926962.45999999</v>
       </c>
       <c r="I84" t="n">
-        <v>100680275.52</v>
+        <v>102186077.57</v>
       </c>
     </row>
     <row r="85">
@@ -3136,13 +3136,13 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>117821880.93</v>
+        <v>118478590.74</v>
       </c>
       <c r="F85" t="n">
-        <v>91470638.66</v>
+        <v>93182948.06</v>
       </c>
       <c r="G85" t="n">
-        <v>76504831.7</v>
+        <v>78576059.76000001</v>
       </c>
       <c r="H85" t="n">
         <v>34371578.38</v>
@@ -3169,13 +3169,13 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>12400021.98</v>
+        <v>13194314.19</v>
       </c>
       <c r="F86" t="n">
-        <v>10400976.78</v>
+        <v>10659970.18</v>
       </c>
       <c r="G86" t="n">
-        <v>9315020.67</v>
+        <v>9722062.060000001</v>
       </c>
       <c r="H86" t="n">
         <v>5551396.54</v>
@@ -3202,13 +3202,13 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6102557.7</v>
+        <v>6112557.7</v>
       </c>
       <c r="F87" t="n">
-        <v>5940690.48</v>
+        <v>5986447.91</v>
       </c>
       <c r="G87" t="n">
-        <v>4489863.8</v>
+        <v>4559748.41</v>
       </c>
       <c r="H87" t="n">
         <v>624962.6800000001</v>
@@ -3235,19 +3235,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>82815025.54000001</v>
+        <v>83501715.89</v>
       </c>
       <c r="F88" t="n">
-        <v>58779811.76</v>
+        <v>59297065.82</v>
       </c>
       <c r="G88" t="n">
-        <v>52142889.58</v>
+        <v>52975405.08</v>
       </c>
       <c r="H88" t="n">
-        <v>21059855.56</v>
+        <v>21251568.16</v>
       </c>
       <c r="I88" t="n">
-        <v>20128479.04</v>
+        <v>20251547.99</v>
       </c>
     </row>
     <row r="89">
@@ -3268,19 +3268,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>68296280.73</v>
+        <v>70155361.22</v>
       </c>
       <c r="F89" t="n">
-        <v>50549207.26</v>
+        <v>51527529.94</v>
       </c>
       <c r="G89" t="n">
-        <v>45417097.1</v>
+        <v>46327558.62</v>
       </c>
       <c r="H89" t="n">
-        <v>26465448.75</v>
+        <v>26558757.44</v>
       </c>
       <c r="I89" t="n">
-        <v>24426555.48</v>
+        <v>24506730.69</v>
       </c>
     </row>
     <row r="90">
@@ -3301,13 +3301,13 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3382956.64</v>
+        <v>3382169.71</v>
       </c>
       <c r="F90" t="n">
-        <v>2379445.01</v>
+        <v>2382840.05</v>
       </c>
       <c r="G90" t="n">
-        <v>2089150.32</v>
+        <v>2090921.88</v>
       </c>
       <c r="H90" t="n">
         <v>294468.9</v>
